--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -917,6 +917,6028 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128458651</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97353</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>679660</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7118198</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128458343</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56864</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>679724</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7118278</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128458646</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>679701</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7118347</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre hack på låga</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128458639</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57833</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>679614</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7118176</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128458393</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>679637</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7118460</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128458355</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>679614</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7118447</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128458379</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58043</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>679582</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7118432</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128458684</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>679669</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7118266</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128458345</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57833</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>679629</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7118222</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128458380</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91376</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>679630</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7118401</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128458666</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98476</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>679677</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7118227</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Blomställning</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128458390</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>679650</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7118244</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128458361</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>679603</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7118423</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128458348</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57833</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>679621</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7118452</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128458352</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>679621</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7118452</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128458392</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>679587</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7118403</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128458400</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>679599</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7118424</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bohål på granlåga</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128458339</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91323</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>679682</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7118294</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128458690</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>679678</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7118225</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128458396</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>679612</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7118334</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128458383</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>679564</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7118347</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128458655</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79056</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>679638</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7118187</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128458688</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>679619</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7118185</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128458686</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>679592</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7118161</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128458360</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>679584</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7118426</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128458347</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57833</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>679582</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7118432</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128458667</v>
+      </c>
+      <c r="B30" t="n">
+        <v>75139</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>679624</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7118176</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128458363</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80163</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>679619</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7118451</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128458397</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>679666</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7118288</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128458683</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>679678</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7118309</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128458649</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>679607</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7118183</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128458395</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>679643</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7118369</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128458689</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>679651</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7118207</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128458341</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>679625</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7118333</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128458650</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>679651</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7118217</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128458669</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>679615</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7118231</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128458357</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>679576</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7118418</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128458685</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>679565</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7118208</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128458354</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>679621</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7118296</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128458338</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91323</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>679591</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7118426</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128458359</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>679602</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7118340</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128458398</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>679689</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7118284</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128458665</v>
+      </c>
+      <c r="B46" t="n">
+        <v>58043</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>679618</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7118186</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>läte</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128458682</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>679705</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7118324</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128458394</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>679604</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7118405</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128458391</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>679610</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7118293</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128472156</v>
+      </c>
+      <c r="B50" t="n">
+        <v>97355</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>679705</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7118311</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128472174</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98395</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>679749</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7118381</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128472170</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>679711</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7118370</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128472149</v>
+      </c>
+      <c r="B53" t="n">
+        <v>92057</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>679727</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7118309</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128472158</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91325</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>679640</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7118398</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128472169</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>679722</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7118390</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128472165</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57777</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>679747</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7118413</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128472166</v>
+      </c>
+      <c r="B57" t="n">
+        <v>58043</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>679731</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7118423</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128472148</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91325</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>679727</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7118380</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128472172</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>679688</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7118409</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128472159</v>
+      </c>
+      <c r="B60" t="n">
+        <v>80163</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>679749</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7118408</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128472157</v>
+      </c>
+      <c r="B61" t="n">
+        <v>97355</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>679659</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7118444</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128472171</v>
+      </c>
+      <c r="B62" t="n">
+        <v>58043</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>679663</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7118432</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128472167</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>679677</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7118405</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128472168</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>679667</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7118389</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128458651</v>
+        <v>128458343</v>
       </c>
       <c r="B4" t="n">
-        <v>97353</v>
+        <v>56864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>679660</v>
+        <v>679724</v>
       </c>
       <c r="R4" t="n">
-        <v>7118198</v>
+        <v>7118278</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128458343</v>
+        <v>128458651</v>
       </c>
       <c r="B5" t="n">
-        <v>56864</v>
+        <v>97355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>679724</v>
+        <v>679660</v>
       </c>
       <c r="R5" t="n">
-        <v>7118278</v>
+        <v>7118198</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128458393</v>
+        <v>128458355</v>
       </c>
       <c r="B8" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1335,34 +1335,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>679637</v>
+        <v>679614</v>
       </c>
       <c r="R8" t="n">
-        <v>7118460</v>
+        <v>7118447</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,6 +1403,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128458355</v>
+        <v>128458393</v>
       </c>
       <c r="B9" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1432,42 +1445,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>679614</v>
+        <v>679637</v>
       </c>
       <c r="R9" t="n">
-        <v>7118447</v>
+        <v>7118460</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,11 +1505,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128458684</v>
+        <v>128458361</v>
       </c>
       <c r="B11" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>679669</v>
+        <v>679603</v>
       </c>
       <c r="R11" t="n">
-        <v>7118266</v>
+        <v>7118423</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,6 +1699,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128458345</v>
+        <v>128458380</v>
       </c>
       <c r="B12" t="n">
-        <v>57833</v>
+        <v>91378</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>679629</v>
+        <v>679630</v>
       </c>
       <c r="R12" t="n">
-        <v>7118222</v>
+        <v>7118401</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,45 +1827,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128458380</v>
+        <v>128458666</v>
       </c>
       <c r="B13" t="n">
-        <v>91376</v>
+        <v>98478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679630</v>
+        <v>679677</v>
       </c>
       <c r="R13" t="n">
-        <v>7118401</v>
+        <v>7118227</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1895,12 +1912,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Blomställning</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1919,57 +1942,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128458666</v>
+        <v>128458684</v>
       </c>
       <c r="B14" t="n">
-        <v>98476</v>
+        <v>79032</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>679677</v>
+        <v>679669</v>
       </c>
       <c r="R14" t="n">
-        <v>7118227</v>
+        <v>7118266</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,18 +2015,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Blomställning</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2131,10 +2136,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128458361</v>
+        <v>128458345</v>
       </c>
       <c r="B16" t="n">
-        <v>57673</v>
+        <v>57833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,21 +2147,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2166,10 +2171,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>679603</v>
+        <v>679629</v>
       </c>
       <c r="R16" t="n">
-        <v>7118423</v>
+        <v>7118222</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,11 +2207,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2330,10 +2330,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128458352</v>
+        <v>128458400</v>
       </c>
       <c r="B18" t="n">
-        <v>57670</v>
+        <v>57673</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2341,16 +2341,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>679621</v>
+        <v>679599</v>
       </c>
       <c r="R18" t="n">
-        <v>7118452</v>
+        <v>7118424</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2401,6 +2401,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2427,32 +2432,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128458392</v>
+        <v>128458339</v>
       </c>
       <c r="B19" t="n">
-        <v>79032</v>
+        <v>91325</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2462,10 +2467,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>679587</v>
+        <v>679682</v>
       </c>
       <c r="R19" t="n">
-        <v>7118403</v>
+        <v>7118294</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2524,10 +2529,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128458400</v>
+        <v>128458352</v>
       </c>
       <c r="B20" t="n">
-        <v>57673</v>
+        <v>57670</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,16 +2540,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2559,10 +2564,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>679599</v>
+        <v>679621</v>
       </c>
       <c r="R20" t="n">
-        <v>7118424</v>
+        <v>7118452</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2595,11 +2600,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2626,32 +2626,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128458339</v>
+        <v>128458392</v>
       </c>
       <c r="B21" t="n">
-        <v>91323</v>
+        <v>79032</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>679682</v>
+        <v>679587</v>
       </c>
       <c r="R21" t="n">
-        <v>7118294</v>
+        <v>7118403</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3117,10 +3117,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128458688</v>
+        <v>128458360</v>
       </c>
       <c r="B26" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3128,21 +3128,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>679619</v>
+        <v>679584</v>
       </c>
       <c r="R26" t="n">
-        <v>7118185</v>
+        <v>7118426</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3188,6 +3188,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3214,7 +3219,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128458686</v>
+        <v>128458688</v>
       </c>
       <c r="B27" t="n">
         <v>79032</v>
@@ -3249,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>679592</v>
+        <v>679619</v>
       </c>
       <c r="R27" t="n">
-        <v>7118161</v>
+        <v>7118185</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3311,10 +3316,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128458360</v>
+        <v>128458686</v>
       </c>
       <c r="B28" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3322,21 +3327,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3346,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>679584</v>
+        <v>679592</v>
       </c>
       <c r="R28" t="n">
-        <v>7118426</v>
+        <v>7118161</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3382,11 +3387,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3413,32 +3413,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128458347</v>
+        <v>128458667</v>
       </c>
       <c r="B29" t="n">
-        <v>57833</v>
+        <v>75139</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6439</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>679582</v>
+        <v>679624</v>
       </c>
       <c r="R29" t="n">
-        <v>7118432</v>
+        <v>7118176</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3510,32 +3510,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128458667</v>
+        <v>128458347</v>
       </c>
       <c r="B30" t="n">
-        <v>75139</v>
+        <v>57833</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6439</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>679624</v>
+        <v>679582</v>
       </c>
       <c r="R30" t="n">
-        <v>7118176</v>
+        <v>7118432</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4097,10 +4097,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458689</v>
+        <v>128458650</v>
       </c>
       <c r="B36" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4135,7 +4135,7 @@
         <v>679651</v>
       </c>
       <c r="R36" t="n">
-        <v>7118207</v>
+        <v>7118217</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4168,6 +4168,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4194,10 +4199,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458341</v>
+        <v>128458689</v>
       </c>
       <c r="B37" t="n">
-        <v>79650</v>
+        <v>79032</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4205,21 +4210,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4229,10 +4234,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679625</v>
+        <v>679651</v>
       </c>
       <c r="R37" t="n">
-        <v>7118333</v>
+        <v>7118207</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4291,10 +4296,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128458650</v>
+        <v>128458341</v>
       </c>
       <c r="B38" t="n">
-        <v>57673</v>
+        <v>79650</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4302,21 +4307,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4326,10 +4331,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679651</v>
+        <v>679625</v>
       </c>
       <c r="R38" t="n">
-        <v>7118217</v>
+        <v>7118333</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4362,11 +4367,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4598,32 +4598,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128458685</v>
+        <v>128458338</v>
       </c>
       <c r="B41" t="n">
-        <v>79032</v>
+        <v>91325</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>679565</v>
+        <v>679591</v>
       </c>
       <c r="R41" t="n">
-        <v>7118208</v>
+        <v>7118426</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4695,27 +4695,27 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128458354</v>
+        <v>128458665</v>
       </c>
       <c r="B42" t="n">
-        <v>57673</v>
+        <v>58043</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679621</v>
+        <v>679618</v>
       </c>
       <c r="R42" t="n">
-        <v>7118296</v>
+        <v>7118186</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>läte</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4797,32 +4797,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128458338</v>
+        <v>128458354</v>
       </c>
       <c r="B43" t="n">
-        <v>91323</v>
+        <v>57673</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4832,10 +4832,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>679591</v>
+        <v>679621</v>
       </c>
       <c r="R43" t="n">
-        <v>7118426</v>
+        <v>7118296</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4868,6 +4868,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4996,7 +5001,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128458398</v>
+        <v>128458685</v>
       </c>
       <c r="B45" t="n">
         <v>79032</v>
@@ -5031,10 +5036,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>679689</v>
+        <v>679565</v>
       </c>
       <c r="R45" t="n">
-        <v>7118284</v>
+        <v>7118208</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5093,32 +5098,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128458665</v>
+        <v>128458398</v>
       </c>
       <c r="B46" t="n">
-        <v>58043</v>
+        <v>79032</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5128,10 +5133,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>679618</v>
+        <v>679689</v>
       </c>
       <c r="R46" t="n">
-        <v>7118186</v>
+        <v>7118284</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5164,11 +5169,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>läte</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5583,32 +5583,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128472174</v>
+        <v>128472170</v>
       </c>
       <c r="B51" t="n">
-        <v>98395</v>
+        <v>79032</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>679749</v>
+        <v>679711</v>
       </c>
       <c r="R51" t="n">
-        <v>7118381</v>
+        <v>7118370</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5680,32 +5680,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128472170</v>
+        <v>128472174</v>
       </c>
       <c r="B52" t="n">
-        <v>79032</v>
+        <v>98395</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5715,10 +5715,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>679711</v>
+        <v>679749</v>
       </c>
       <c r="R52" t="n">
-        <v>7118370</v>
+        <v>7118381</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6747,7 +6747,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128472167</v>
+        <v>128472168</v>
       </c>
       <c r="B63" t="n">
         <v>79032</v>
@@ -6782,10 +6782,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>679677</v>
+        <v>679667</v>
       </c>
       <c r="R63" t="n">
-        <v>7118405</v>
+        <v>7118389</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6844,7 +6844,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128472168</v>
+        <v>128472167</v>
       </c>
       <c r="B64" t="n">
         <v>79032</v>
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>679667</v>
+        <v>679677</v>
       </c>
       <c r="R64" t="n">
-        <v>7118389</v>
+        <v>7118405</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1827,57 +1827,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128458666</v>
+        <v>128458684</v>
       </c>
       <c r="B13" t="n">
-        <v>98478</v>
+        <v>79032</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679677</v>
+        <v>679669</v>
       </c>
       <c r="R13" t="n">
-        <v>7118227</v>
+        <v>7118266</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,18 +1900,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Blomställning</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1942,7 +1924,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128458684</v>
+        <v>128458390</v>
       </c>
       <c r="B14" t="n">
         <v>79032</v>
@@ -1977,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>679669</v>
+        <v>679650</v>
       </c>
       <c r="R14" t="n">
-        <v>7118266</v>
+        <v>7118244</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,45 +2021,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128458390</v>
+        <v>128458666</v>
       </c>
       <c r="B15" t="n">
-        <v>79032</v>
+        <v>98478</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>679650</v>
+        <v>679677</v>
       </c>
       <c r="R15" t="n">
-        <v>7118244</v>
+        <v>7118227</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,12 +2106,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Blomställning</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2330,32 +2330,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128458400</v>
+        <v>128458339</v>
       </c>
       <c r="B18" t="n">
-        <v>57673</v>
+        <v>91325</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>679599</v>
+        <v>679682</v>
       </c>
       <c r="R18" t="n">
-        <v>7118424</v>
+        <v>7118294</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2401,11 +2401,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2432,32 +2427,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128458339</v>
+        <v>128458352</v>
       </c>
       <c r="B19" t="n">
-        <v>91325</v>
+        <v>57670</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2467,10 +2462,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>679682</v>
+        <v>679621</v>
       </c>
       <c r="R19" t="n">
-        <v>7118294</v>
+        <v>7118452</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2529,10 +2524,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128458352</v>
+        <v>128458392</v>
       </c>
       <c r="B20" t="n">
-        <v>57670</v>
+        <v>79032</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2540,21 +2535,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2564,10 +2559,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>679621</v>
+        <v>679587</v>
       </c>
       <c r="R20" t="n">
-        <v>7118452</v>
+        <v>7118403</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2626,10 +2621,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128458392</v>
+        <v>128458400</v>
       </c>
       <c r="B21" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2637,21 +2632,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2661,10 +2656,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>679587</v>
+        <v>679599</v>
       </c>
       <c r="R21" t="n">
-        <v>7118403</v>
+        <v>7118424</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2697,6 +2692,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3020,32 +3020,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128458655</v>
+        <v>128458360</v>
       </c>
       <c r="B25" t="n">
-        <v>79056</v>
+        <v>57673</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>679638</v>
+        <v>679584</v>
       </c>
       <c r="R25" t="n">
-        <v>7118187</v>
+        <v>7118426</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3091,6 +3091,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3117,10 +3122,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128458360</v>
+        <v>128458688</v>
       </c>
       <c r="B26" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3128,21 +3133,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3152,10 +3157,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>679584</v>
+        <v>679619</v>
       </c>
       <c r="R26" t="n">
-        <v>7118426</v>
+        <v>7118185</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3188,11 +3193,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3219,7 +3219,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128458688</v>
+        <v>128458686</v>
       </c>
       <c r="B27" t="n">
         <v>79032</v>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>679619</v>
+        <v>679592</v>
       </c>
       <c r="R27" t="n">
-        <v>7118185</v>
+        <v>7118161</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3316,32 +3316,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128458686</v>
+        <v>128458667</v>
       </c>
       <c r="B28" t="n">
-        <v>79032</v>
+        <v>75139</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>679592</v>
+        <v>679624</v>
       </c>
       <c r="R28" t="n">
-        <v>7118161</v>
+        <v>7118176</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3413,32 +3413,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128458667</v>
+        <v>128458347</v>
       </c>
       <c r="B29" t="n">
-        <v>75139</v>
+        <v>57833</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6439</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>679624</v>
+        <v>679582</v>
       </c>
       <c r="R29" t="n">
-        <v>7118176</v>
+        <v>7118432</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3510,32 +3510,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128458347</v>
+        <v>128458363</v>
       </c>
       <c r="B30" t="n">
-        <v>57833</v>
+        <v>80163</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>679582</v>
+        <v>679619</v>
       </c>
       <c r="R30" t="n">
-        <v>7118432</v>
+        <v>7118451</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3607,32 +3607,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128458363</v>
+        <v>128458397</v>
       </c>
       <c r="B31" t="n">
-        <v>80163</v>
+        <v>79032</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>679619</v>
+        <v>679666</v>
       </c>
       <c r="R31" t="n">
-        <v>7118451</v>
+        <v>7118288</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3704,7 +3704,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128458397</v>
+        <v>128458683</v>
       </c>
       <c r="B32" t="n">
         <v>79032</v>
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>679666</v>
+        <v>679678</v>
       </c>
       <c r="R32" t="n">
-        <v>7118288</v>
+        <v>7118309</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3801,10 +3801,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128458683</v>
+        <v>128458649</v>
       </c>
       <c r="B33" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3812,21 +3812,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>679678</v>
+        <v>679607</v>
       </c>
       <c r="R33" t="n">
-        <v>7118309</v>
+        <v>7118183</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3872,6 +3872,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3898,10 +3903,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128458649</v>
+        <v>128458395</v>
       </c>
       <c r="B34" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3909,21 +3914,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3933,10 +3938,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>679607</v>
+        <v>679643</v>
       </c>
       <c r="R34" t="n">
-        <v>7118183</v>
+        <v>7118369</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3969,11 +3974,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4000,10 +4000,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458395</v>
+        <v>128458650</v>
       </c>
       <c r="B35" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4011,21 +4011,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>679643</v>
+        <v>679651</v>
       </c>
       <c r="R35" t="n">
-        <v>7118369</v>
+        <v>7118217</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4071,6 +4071,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4097,10 +4102,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458650</v>
+        <v>128458689</v>
       </c>
       <c r="B36" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4108,21 +4113,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4135,7 +4140,7 @@
         <v>679651</v>
       </c>
       <c r="R36" t="n">
-        <v>7118217</v>
+        <v>7118207</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4168,11 +4173,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4199,10 +4199,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458689</v>
+        <v>128458341</v>
       </c>
       <c r="B37" t="n">
-        <v>79032</v>
+        <v>79650</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4210,21 +4210,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679651</v>
+        <v>679625</v>
       </c>
       <c r="R37" t="n">
-        <v>7118207</v>
+        <v>7118333</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4296,10 +4296,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128458341</v>
+        <v>128458669</v>
       </c>
       <c r="B38" t="n">
-        <v>79650</v>
+        <v>79032</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4307,21 +4307,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679625</v>
+        <v>679615</v>
       </c>
       <c r="R38" t="n">
-        <v>7118333</v>
+        <v>7118231</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4369,12 +4369,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4393,10 +4399,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128458669</v>
+        <v>128458357</v>
       </c>
       <c r="B39" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4404,21 +4410,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4428,10 +4434,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>679615</v>
+        <v>679576</v>
       </c>
       <c r="R39" t="n">
-        <v>7118231</v>
+        <v>7118418</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4468,7 +4474,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Med apotecier</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4477,7 +4483,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4496,32 +4501,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128458357</v>
+        <v>128458338</v>
       </c>
       <c r="B40" t="n">
-        <v>57673</v>
+        <v>91325</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4531,10 +4536,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>679576</v>
+        <v>679591</v>
       </c>
       <c r="R40" t="n">
-        <v>7118418</v>
+        <v>7118426</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4567,11 +4572,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4598,32 +4598,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128458338</v>
+        <v>128458685</v>
       </c>
       <c r="B41" t="n">
-        <v>91325</v>
+        <v>79032</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>679591</v>
+        <v>679565</v>
       </c>
       <c r="R41" t="n">
-        <v>7118426</v>
+        <v>7118208</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4695,32 +4695,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128458665</v>
+        <v>128458398</v>
       </c>
       <c r="B42" t="n">
-        <v>58043</v>
+        <v>79032</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679618</v>
+        <v>679689</v>
       </c>
       <c r="R42" t="n">
-        <v>7118186</v>
+        <v>7118284</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4766,11 +4766,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>läte</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5001,32 +4996,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128458685</v>
+        <v>128458665</v>
       </c>
       <c r="B45" t="n">
-        <v>79032</v>
+        <v>58043</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5036,10 +5031,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>679565</v>
+        <v>679618</v>
       </c>
       <c r="R45" t="n">
-        <v>7118208</v>
+        <v>7118186</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5072,6 +5067,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>läte</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5098,7 +5098,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128458398</v>
+        <v>128458682</v>
       </c>
       <c r="B46" t="n">
         <v>79032</v>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>679689</v>
+        <v>679705</v>
       </c>
       <c r="R46" t="n">
-        <v>7118284</v>
+        <v>7118324</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5195,7 +5195,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128458682</v>
+        <v>128458394</v>
       </c>
       <c r="B47" t="n">
         <v>79032</v>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>679705</v>
+        <v>679604</v>
       </c>
       <c r="R47" t="n">
-        <v>7118324</v>
+        <v>7118405</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5292,7 +5292,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128458394</v>
+        <v>128458391</v>
       </c>
       <c r="B48" t="n">
         <v>79032</v>
@@ -5327,10 +5327,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>679604</v>
+        <v>679610</v>
       </c>
       <c r="R48" t="n">
-        <v>7118405</v>
+        <v>7118293</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5389,32 +5389,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128458391</v>
+        <v>128472156</v>
       </c>
       <c r="B49" t="n">
-        <v>79032</v>
+        <v>97355</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>679610</v>
+        <v>679705</v>
       </c>
       <c r="R49" t="n">
-        <v>7118293</v>
+        <v>7118311</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5474,44 +5474,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Felix Gustafsson</t>
+          <t>Felix Gustafsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128472156</v>
+        <v>128472170</v>
       </c>
       <c r="B50" t="n">
-        <v>97355</v>
+        <v>79032</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5521,10 +5521,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>679705</v>
+        <v>679711</v>
       </c>
       <c r="R50" t="n">
-        <v>7118311</v>
+        <v>7118370</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5583,32 +5583,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128472170</v>
+        <v>128472174</v>
       </c>
       <c r="B51" t="n">
-        <v>79032</v>
+        <v>98395</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>679711</v>
+        <v>679749</v>
       </c>
       <c r="R51" t="n">
-        <v>7118370</v>
+        <v>7118381</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5680,10 +5680,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128472174</v>
+        <v>128472149</v>
       </c>
       <c r="B52" t="n">
-        <v>98395</v>
+        <v>92057</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5691,21 +5691,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219790</v>
+        <v>3298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5715,10 +5715,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>679749</v>
+        <v>679727</v>
       </c>
       <c r="R52" t="n">
-        <v>7118381</v>
+        <v>7118309</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5777,10 +5777,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128472149</v>
+        <v>128472158</v>
       </c>
       <c r="B53" t="n">
-        <v>92057</v>
+        <v>91325</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5788,21 +5788,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>679727</v>
+        <v>679640</v>
       </c>
       <c r="R53" t="n">
-        <v>7118309</v>
+        <v>7118398</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5874,32 +5874,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128472158</v>
+        <v>128472169</v>
       </c>
       <c r="B54" t="n">
-        <v>91325</v>
+        <v>79032</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5909,10 +5909,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>679640</v>
+        <v>679722</v>
       </c>
       <c r="R54" t="n">
-        <v>7118398</v>
+        <v>7118390</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5971,32 +5971,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128472169</v>
+        <v>128472165</v>
       </c>
       <c r="B55" t="n">
-        <v>79032</v>
+        <v>57777</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6006,10 +6006,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>679722</v>
+        <v>679747</v>
       </c>
       <c r="R55" t="n">
-        <v>7118390</v>
+        <v>7118413</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6068,10 +6068,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128472165</v>
+        <v>128472166</v>
       </c>
       <c r="B56" t="n">
-        <v>57777</v>
+        <v>58043</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6079,16 +6079,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103031</v>
+        <v>103015</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6103,10 +6103,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>679747</v>
+        <v>679731</v>
       </c>
       <c r="R56" t="n">
-        <v>7118413</v>
+        <v>7118423</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6165,10 +6165,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128472166</v>
+        <v>128472148</v>
       </c>
       <c r="B57" t="n">
-        <v>58043</v>
+        <v>91325</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6176,21 +6176,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6200,10 +6200,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>679731</v>
+        <v>679727</v>
       </c>
       <c r="R57" t="n">
-        <v>7118423</v>
+        <v>7118380</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6262,32 +6262,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128472148</v>
+        <v>128472172</v>
       </c>
       <c r="B58" t="n">
-        <v>91325</v>
+        <v>79032</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6297,10 +6297,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>679727</v>
+        <v>679688</v>
       </c>
       <c r="R58" t="n">
-        <v>7118380</v>
+        <v>7118409</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6359,32 +6359,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128472172</v>
+        <v>128472159</v>
       </c>
       <c r="B59" t="n">
-        <v>79032</v>
+        <v>80163</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6394,10 +6394,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>679688</v>
+        <v>679749</v>
       </c>
       <c r="R59" t="n">
-        <v>7118409</v>
+        <v>7118408</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6456,10 +6456,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128472159</v>
+        <v>128472157</v>
       </c>
       <c r="B60" t="n">
-        <v>80163</v>
+        <v>97355</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6467,21 +6467,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6491,10 +6491,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>679749</v>
+        <v>679659</v>
       </c>
       <c r="R60" t="n">
-        <v>7118408</v>
+        <v>7118444</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6553,10 +6553,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128472157</v>
+        <v>128472171</v>
       </c>
       <c r="B61" t="n">
-        <v>97355</v>
+        <v>58043</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6564,21 +6564,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>679659</v>
+        <v>679663</v>
       </c>
       <c r="R61" t="n">
-        <v>7118444</v>
+        <v>7118432</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6650,32 +6650,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128472171</v>
+        <v>128472168</v>
       </c>
       <c r="B62" t="n">
-        <v>58043</v>
+        <v>79032</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6685,10 +6685,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>679663</v>
+        <v>679667</v>
       </c>
       <c r="R62" t="n">
-        <v>7118432</v>
+        <v>7118389</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6747,7 +6747,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128472168</v>
+        <v>128472167</v>
       </c>
       <c r="B63" t="n">
         <v>79032</v>
@@ -6782,10 +6782,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>679667</v>
+        <v>679677</v>
       </c>
       <c r="R63" t="n">
-        <v>7118389</v>
+        <v>7118405</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6841,103 +6841,6 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>128472167</v>
-      </c>
-      <c r="B64" t="n">
-        <v>79032</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Gålgoberget, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>679677</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7118405</v>
-      </c>
-      <c r="S64" t="n">
-        <v>10</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Örträsk</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Felix Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Felix Gustafsson, Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128458343</v>
+        <v>128458651</v>
       </c>
       <c r="B4" t="n">
-        <v>56864</v>
+        <v>97448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>679724</v>
+        <v>679660</v>
       </c>
       <c r="R4" t="n">
-        <v>7118278</v>
+        <v>7118198</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128458651</v>
+        <v>128458343</v>
       </c>
       <c r="B5" t="n">
-        <v>97355</v>
+        <v>56876</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>679660</v>
+        <v>679724</v>
       </c>
       <c r="R5" t="n">
-        <v>7118198</v>
+        <v>7118278</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,7 +1116,7 @@
         <v>128458646</v>
       </c>
       <c r="B6" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128458639</v>
       </c>
       <c r="B7" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128458355</v>
+        <v>128458393</v>
       </c>
       <c r="B8" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1335,42 +1335,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>679614</v>
+        <v>679637</v>
       </c>
       <c r="R8" t="n">
-        <v>7118447</v>
+        <v>7118460</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,11 +1395,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128458393</v>
+        <v>128458355</v>
       </c>
       <c r="B9" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,34 +1432,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>679637</v>
+        <v>679614</v>
       </c>
       <c r="R9" t="n">
-        <v>7118460</v>
+        <v>7118447</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,6 +1500,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,7 +1534,7 @@
         <v>128458379</v>
       </c>
       <c r="B10" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128458361</v>
+        <v>128458380</v>
       </c>
       <c r="B11" t="n">
-        <v>57673</v>
+        <v>91470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>679603</v>
+        <v>679630</v>
       </c>
       <c r="R11" t="n">
-        <v>7118423</v>
+        <v>7118401</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1699,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128458380</v>
+        <v>128458361</v>
       </c>
       <c r="B12" t="n">
-        <v>91378</v>
+        <v>57685</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>679630</v>
+        <v>679603</v>
       </c>
       <c r="R12" t="n">
-        <v>7118401</v>
+        <v>7118423</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,6 +1796,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,45 +1827,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128458684</v>
+        <v>128458666</v>
       </c>
       <c r="B13" t="n">
-        <v>79032</v>
+        <v>98571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679669</v>
+        <v>679677</v>
       </c>
       <c r="R13" t="n">
-        <v>7118266</v>
+        <v>7118227</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,12 +1912,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Blomställning</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1924,10 +1942,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128458390</v>
+        <v>128458684</v>
       </c>
       <c r="B14" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,10 +1977,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>679650</v>
+        <v>679669</v>
       </c>
       <c r="R14" t="n">
-        <v>7118244</v>
+        <v>7118266</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,57 +2039,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128458666</v>
+        <v>128458390</v>
       </c>
       <c r="B15" t="n">
-        <v>98478</v>
+        <v>79083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>679677</v>
+        <v>679650</v>
       </c>
       <c r="R15" t="n">
-        <v>7118227</v>
+        <v>7118244</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2106,18 +2112,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Blomställning</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2139,7 +2139,7 @@
         <v>128458345</v>
       </c>
       <c r="B16" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>128458348</v>
       </c>
       <c r="B17" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>128458339</v>
       </c>
       <c r="B18" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>128458352</v>
       </c>
       <c r="B19" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>128458392</v>
       </c>
       <c r="B20" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>128458400</v>
       </c>
       <c r="B21" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>128458690</v>
       </c>
       <c r="B22" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>128458396</v>
       </c>
       <c r="B23" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>128458383</v>
       </c>
       <c r="B24" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3020,10 +3020,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128458360</v>
+        <v>128458688</v>
       </c>
       <c r="B25" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3031,21 +3031,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>679584</v>
+        <v>679619</v>
       </c>
       <c r="R25" t="n">
-        <v>7118426</v>
+        <v>7118185</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3091,11 +3091,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3122,10 +3117,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128458688</v>
+        <v>128458686</v>
       </c>
       <c r="B26" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3157,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>679619</v>
+        <v>679592</v>
       </c>
       <c r="R26" t="n">
-        <v>7118185</v>
+        <v>7118161</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3219,10 +3214,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128458686</v>
+        <v>128458360</v>
       </c>
       <c r="B27" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3230,21 +3225,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3254,10 +3249,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>679592</v>
+        <v>679584</v>
       </c>
       <c r="R27" t="n">
-        <v>7118161</v>
+        <v>7118426</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3290,6 +3285,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3319,7 +3319,7 @@
         <v>128458667</v>
       </c>
       <c r="B28" t="n">
-        <v>75139</v>
+        <v>75154</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>128458347</v>
       </c>
       <c r="B29" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>128458363</v>
       </c>
       <c r="B30" t="n">
-        <v>80163</v>
+        <v>80216</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>128458397</v>
       </c>
       <c r="B31" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>128458683</v>
       </c>
       <c r="B32" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3801,10 +3801,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128458649</v>
+        <v>128458395</v>
       </c>
       <c r="B33" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3812,21 +3812,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>679607</v>
+        <v>679643</v>
       </c>
       <c r="R33" t="n">
-        <v>7118183</v>
+        <v>7118369</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3872,11 +3872,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3903,10 +3898,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128458395</v>
+        <v>128458649</v>
       </c>
       <c r="B34" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,21 +3909,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,10 +3933,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>679643</v>
+        <v>679607</v>
       </c>
       <c r="R34" t="n">
-        <v>7118369</v>
+        <v>7118183</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3974,6 +3969,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4000,10 +4000,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458650</v>
+        <v>128458689</v>
       </c>
       <c r="B35" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4011,21 +4011,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4038,7 +4038,7 @@
         <v>679651</v>
       </c>
       <c r="R35" t="n">
-        <v>7118217</v>
+        <v>7118207</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4071,11 +4071,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4102,10 +4097,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458689</v>
+        <v>128458341</v>
       </c>
       <c r="B36" t="n">
-        <v>79032</v>
+        <v>79702</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4113,21 +4108,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4137,10 +4132,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679651</v>
+        <v>679625</v>
       </c>
       <c r="R36" t="n">
-        <v>7118207</v>
+        <v>7118333</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4199,10 +4194,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458341</v>
+        <v>128458669</v>
       </c>
       <c r="B37" t="n">
-        <v>79650</v>
+        <v>79083</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4210,21 +4205,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4234,10 +4229,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679625</v>
+        <v>679615</v>
       </c>
       <c r="R37" t="n">
-        <v>7118333</v>
+        <v>7118231</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4272,12 +4267,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4296,10 +4297,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128458669</v>
+        <v>128458650</v>
       </c>
       <c r="B38" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4307,21 +4308,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4331,10 +4332,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679615</v>
+        <v>679651</v>
       </c>
       <c r="R38" t="n">
-        <v>7118231</v>
+        <v>7118217</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4371,7 +4372,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Med apotecier</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4380,7 +4381,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4402,7 +4402,7 @@
         <v>128458357</v>
       </c>
       <c r="B39" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4501,32 +4501,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128458338</v>
+        <v>128458685</v>
       </c>
       <c r="B40" t="n">
-        <v>91325</v>
+        <v>79083</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>679591</v>
+        <v>679565</v>
       </c>
       <c r="R40" t="n">
-        <v>7118426</v>
+        <v>7118208</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4598,10 +4598,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128458685</v>
+        <v>128458398</v>
       </c>
       <c r="B41" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>679565</v>
+        <v>679689</v>
       </c>
       <c r="R41" t="n">
-        <v>7118208</v>
+        <v>7118284</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4695,10 +4695,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128458398</v>
+        <v>128458354</v>
       </c>
       <c r="B42" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4706,21 +4706,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679689</v>
+        <v>679621</v>
       </c>
       <c r="R42" t="n">
-        <v>7118284</v>
+        <v>7118296</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4766,6 +4766,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4792,10 +4797,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128458354</v>
+        <v>128458359</v>
       </c>
       <c r="B43" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4827,10 +4832,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>679621</v>
+        <v>679602</v>
       </c>
       <c r="R43" t="n">
-        <v>7118296</v>
+        <v>7118340</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,7 +4872,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4894,27 +4899,27 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128458359</v>
+        <v>128458665</v>
       </c>
       <c r="B44" t="n">
-        <v>57673</v>
+        <v>58055</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4929,10 +4934,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>679602</v>
+        <v>679618</v>
       </c>
       <c r="R44" t="n">
-        <v>7118340</v>
+        <v>7118186</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4969,7 +4974,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>läte</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4996,10 +5001,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128458665</v>
+        <v>128458338</v>
       </c>
       <c r="B45" t="n">
-        <v>58043</v>
+        <v>91417</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5007,21 +5012,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5031,10 +5036,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>679618</v>
+        <v>679591</v>
       </c>
       <c r="R45" t="n">
-        <v>7118186</v>
+        <v>7118426</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5067,11 +5072,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>läte</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5101,7 +5101,7 @@
         <v>128458682</v>
       </c>
       <c r="B46" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>128458394</v>
       </c>
       <c r="B47" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>128458391</v>
       </c>
       <c r="B48" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6842,6 +6842,107 @@
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128501348</v>
+      </c>
+      <c r="B64" t="n">
+        <v>75171</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Gålgoberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>679619</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7118446</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128458651</v>
+        <v>128458343</v>
       </c>
       <c r="B4" t="n">
-        <v>97448</v>
+        <v>56876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>679660</v>
+        <v>679724</v>
       </c>
       <c r="R4" t="n">
-        <v>7118198</v>
+        <v>7118278</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128458343</v>
+        <v>128458651</v>
       </c>
       <c r="B5" t="n">
-        <v>56876</v>
+        <v>97448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>679724</v>
+        <v>679660</v>
       </c>
       <c r="R5" t="n">
-        <v>7118278</v>
+        <v>7118198</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1725,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128458361</v>
+        <v>128458684</v>
       </c>
       <c r="B12" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>679603</v>
+        <v>679669</v>
       </c>
       <c r="R12" t="n">
-        <v>7118423</v>
+        <v>7118266</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,11 +1796,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,57 +1822,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128458666</v>
+        <v>128458390</v>
       </c>
       <c r="B13" t="n">
-        <v>98571</v>
+        <v>79083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679677</v>
+        <v>679650</v>
       </c>
       <c r="R13" t="n">
-        <v>7118227</v>
+        <v>7118244</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,18 +1895,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Blomställning</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1942,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128458684</v>
+        <v>128458361</v>
       </c>
       <c r="B14" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1953,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1977,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>679669</v>
+        <v>679603</v>
       </c>
       <c r="R14" t="n">
-        <v>7118266</v>
+        <v>7118423</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2013,6 +1990,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2039,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128458390</v>
+        <v>128458345</v>
       </c>
       <c r="B15" t="n">
-        <v>79083</v>
+        <v>57845</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2050,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2074,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>679650</v>
+        <v>679629</v>
       </c>
       <c r="R15" t="n">
-        <v>7118244</v>
+        <v>7118222</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,45 +2118,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128458345</v>
+        <v>128458666</v>
       </c>
       <c r="B16" t="n">
-        <v>57845</v>
+        <v>98571</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>679629</v>
+        <v>679677</v>
       </c>
       <c r="R16" t="n">
-        <v>7118222</v>
+        <v>7118227</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,12 +2203,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Blomställning</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2330,32 +2330,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128458339</v>
+        <v>128458392</v>
       </c>
       <c r="B18" t="n">
-        <v>91417</v>
+        <v>79083</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>679682</v>
+        <v>679587</v>
       </c>
       <c r="R18" t="n">
-        <v>7118294</v>
+        <v>7118403</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,32 +2427,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128458352</v>
+        <v>128458339</v>
       </c>
       <c r="B19" t="n">
-        <v>57682</v>
+        <v>91417</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>679621</v>
+        <v>679682</v>
       </c>
       <c r="R19" t="n">
-        <v>7118452</v>
+        <v>7118294</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128458392</v>
+        <v>128458352</v>
       </c>
       <c r="B20" t="n">
-        <v>79083</v>
+        <v>57682</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>679587</v>
+        <v>679621</v>
       </c>
       <c r="R20" t="n">
-        <v>7118403</v>
+        <v>7118452</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -4501,32 +4501,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128458685</v>
+        <v>128458338</v>
       </c>
       <c r="B40" t="n">
-        <v>79083</v>
+        <v>91417</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>679565</v>
+        <v>679591</v>
       </c>
       <c r="R40" t="n">
-        <v>7118208</v>
+        <v>7118426</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4598,7 +4598,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128458398</v>
+        <v>128458685</v>
       </c>
       <c r="B41" t="n">
         <v>79083</v>
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>679689</v>
+        <v>679565</v>
       </c>
       <c r="R41" t="n">
-        <v>7118284</v>
+        <v>7118208</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4695,10 +4695,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128458354</v>
+        <v>128458398</v>
       </c>
       <c r="B42" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4706,21 +4706,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679621</v>
+        <v>679689</v>
       </c>
       <c r="R42" t="n">
-        <v>7118296</v>
+        <v>7118284</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4766,11 +4766,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4797,7 +4792,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128458359</v>
+        <v>128458354</v>
       </c>
       <c r="B43" t="n">
         <v>57685</v>
@@ -4832,10 +4827,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>679602</v>
+        <v>679621</v>
       </c>
       <c r="R43" t="n">
-        <v>7118340</v>
+        <v>7118296</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4872,7 +4867,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4899,27 +4894,27 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128458665</v>
+        <v>128458359</v>
       </c>
       <c r="B44" t="n">
-        <v>58055</v>
+        <v>57685</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4934,10 +4929,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>679618</v>
+        <v>679602</v>
       </c>
       <c r="R44" t="n">
-        <v>7118186</v>
+        <v>7118340</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4974,7 +4969,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>läte</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5001,10 +4996,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128458338</v>
+        <v>128458665</v>
       </c>
       <c r="B45" t="n">
-        <v>91417</v>
+        <v>58055</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5012,21 +5007,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>103015</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5036,10 +5031,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>679591</v>
+        <v>679618</v>
       </c>
       <c r="R45" t="n">
-        <v>7118426</v>
+        <v>7118186</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5072,6 +5067,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>läte</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5392,7 +5392,7 @@
         <v>128472156</v>
       </c>
       <c r="B49" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>128472170</v>
       </c>
       <c r="B50" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>128472174</v>
       </c>
       <c r="B51" t="n">
-        <v>98395</v>
+        <v>98488</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>128472149</v>
       </c>
       <c r="B52" t="n">
-        <v>92057</v>
+        <v>92149</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>128472158</v>
       </c>
       <c r="B53" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>128472169</v>
       </c>
       <c r="B54" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>128472165</v>
       </c>
       <c r="B55" t="n">
-        <v>57777</v>
+        <v>57789</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>128472166</v>
       </c>
       <c r="B56" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>128472148</v>
       </c>
       <c r="B57" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>128472172</v>
       </c>
       <c r="B58" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>128472159</v>
       </c>
       <c r="B59" t="n">
-        <v>80163</v>
+        <v>80216</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>128472157</v>
       </c>
       <c r="B60" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>128472171</v>
       </c>
       <c r="B61" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>128472168</v>
       </c>
       <c r="B62" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>128472167</v>
       </c>
       <c r="B63" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -2330,32 +2330,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128458392</v>
+        <v>128458339</v>
       </c>
       <c r="B18" t="n">
-        <v>79083</v>
+        <v>91417</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>679587</v>
+        <v>679682</v>
       </c>
       <c r="R18" t="n">
-        <v>7118403</v>
+        <v>7118294</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,32 +2427,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128458339</v>
+        <v>128458352</v>
       </c>
       <c r="B19" t="n">
-        <v>91417</v>
+        <v>57682</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>679682</v>
+        <v>679621</v>
       </c>
       <c r="R19" t="n">
-        <v>7118294</v>
+        <v>7118452</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128458352</v>
+        <v>128458400</v>
       </c>
       <c r="B20" t="n">
-        <v>57682</v>
+        <v>57685</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,16 +2535,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>679621</v>
+        <v>679599</v>
       </c>
       <c r="R20" t="n">
-        <v>7118452</v>
+        <v>7118424</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2595,6 +2595,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2621,10 +2626,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128458400</v>
+        <v>128458392</v>
       </c>
       <c r="B21" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2632,21 +2637,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2656,10 +2661,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>679599</v>
+        <v>679587</v>
       </c>
       <c r="R21" t="n">
-        <v>7118424</v>
+        <v>7118403</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2692,11 +2697,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3316,32 +3316,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128458667</v>
+        <v>128458347</v>
       </c>
       <c r="B28" t="n">
-        <v>75154</v>
+        <v>57845</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6439</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>679624</v>
+        <v>679582</v>
       </c>
       <c r="R28" t="n">
-        <v>7118176</v>
+        <v>7118432</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3413,32 +3413,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128458347</v>
+        <v>128458667</v>
       </c>
       <c r="B29" t="n">
-        <v>57845</v>
+        <v>75154</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6439</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>679582</v>
+        <v>679624</v>
       </c>
       <c r="R29" t="n">
-        <v>7118432</v>
+        <v>7118176</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -5392,7 +5392,7 @@
         <v>128472156</v>
       </c>
       <c r="B49" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>128472170</v>
       </c>
       <c r="B50" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>128472174</v>
       </c>
       <c r="B51" t="n">
-        <v>98488</v>
+        <v>98496</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>128472149</v>
       </c>
       <c r="B52" t="n">
-        <v>92149</v>
+        <v>92155</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>128472158</v>
       </c>
       <c r="B53" t="n">
-        <v>91417</v>
+        <v>91423</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>128472169</v>
       </c>
       <c r="B54" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>128472165</v>
       </c>
       <c r="B55" t="n">
-        <v>57789</v>
+        <v>57793</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>128472166</v>
       </c>
       <c r="B56" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>128472148</v>
       </c>
       <c r="B57" t="n">
-        <v>91417</v>
+        <v>91423</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>128472172</v>
       </c>
       <c r="B58" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>128472159</v>
       </c>
       <c r="B59" t="n">
-        <v>80216</v>
+        <v>80220</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>128472157</v>
       </c>
       <c r="B60" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>128472171</v>
       </c>
       <c r="B61" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>128472168</v>
       </c>
       <c r="B62" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>128472167</v>
       </c>
       <c r="B63" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>128501348</v>
       </c>
       <c r="B64" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>128458343</v>
       </c>
       <c r="B4" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>128458651</v>
       </c>
       <c r="B5" t="n">
-        <v>97448</v>
+        <v>97460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>128458646</v>
       </c>
       <c r="B6" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128458639</v>
       </c>
       <c r="B7" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>128458393</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>128458355</v>
       </c>
       <c r="B9" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>128458379</v>
       </c>
       <c r="B10" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>128458380</v>
       </c>
       <c r="B11" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>128458684</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>128458390</v>
       </c>
       <c r="B13" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>128458361</v>
       </c>
       <c r="B14" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>128458345</v>
       </c>
       <c r="B15" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>128458666</v>
       </c>
       <c r="B16" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>128458348</v>
       </c>
       <c r="B17" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,32 +2330,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128458339</v>
+        <v>128458392</v>
       </c>
       <c r="B18" t="n">
-        <v>91417</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>679682</v>
+        <v>679587</v>
       </c>
       <c r="R18" t="n">
-        <v>7118294</v>
+        <v>7118403</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128458352</v>
+        <v>128458400</v>
       </c>
       <c r="B19" t="n">
-        <v>57682</v>
+        <v>57689</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2438,16 +2438,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>679621</v>
+        <v>679599</v>
       </c>
       <c r="R19" t="n">
-        <v>7118452</v>
+        <v>7118424</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2498,6 +2498,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2524,10 +2529,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128458400</v>
+        <v>128458352</v>
       </c>
       <c r="B20" t="n">
-        <v>57685</v>
+        <v>57686</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,16 +2540,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2559,10 +2564,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>679599</v>
+        <v>679621</v>
       </c>
       <c r="R20" t="n">
-        <v>7118424</v>
+        <v>7118452</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2595,11 +2600,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2626,32 +2626,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128458392</v>
+        <v>128458339</v>
       </c>
       <c r="B21" t="n">
-        <v>79083</v>
+        <v>91429</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>679587</v>
+        <v>679682</v>
       </c>
       <c r="R21" t="n">
-        <v>7118403</v>
+        <v>7118294</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2726,7 +2726,7 @@
         <v>128458690</v>
       </c>
       <c r="B22" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>128458396</v>
       </c>
       <c r="B23" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>128458383</v>
       </c>
       <c r="B24" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>128458688</v>
       </c>
       <c r="B25" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>128458686</v>
       </c>
       <c r="B26" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>128458360</v>
       </c>
       <c r="B27" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3316,32 +3316,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128458347</v>
+        <v>128458667</v>
       </c>
       <c r="B28" t="n">
-        <v>57845</v>
+        <v>75158</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6439</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>679582</v>
+        <v>679624</v>
       </c>
       <c r="R28" t="n">
-        <v>7118432</v>
+        <v>7118176</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3413,32 +3413,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128458667</v>
+        <v>128458347</v>
       </c>
       <c r="B29" t="n">
-        <v>75154</v>
+        <v>57849</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6439</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>679624</v>
+        <v>679582</v>
       </c>
       <c r="R29" t="n">
-        <v>7118176</v>
+        <v>7118432</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3513,7 +3513,7 @@
         <v>128458363</v>
       </c>
       <c r="B30" t="n">
-        <v>80216</v>
+        <v>80220</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>128458397</v>
       </c>
       <c r="B31" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>128458683</v>
       </c>
       <c r="B32" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>128458395</v>
       </c>
       <c r="B33" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>128458649</v>
       </c>
       <c r="B34" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>128458689</v>
       </c>
       <c r="B35" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>128458341</v>
       </c>
       <c r="B36" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>128458669</v>
       </c>
       <c r="B37" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>128458650</v>
       </c>
       <c r="B38" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>128458357</v>
       </c>
       <c r="B39" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>128458338</v>
       </c>
       <c r="B40" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>128458685</v>
       </c>
       <c r="B41" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>128458398</v>
       </c>
       <c r="B42" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>128458354</v>
       </c>
       <c r="B43" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>128458359</v>
       </c>
       <c r="B44" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>128458665</v>
       </c>
       <c r="B45" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>128458682</v>
       </c>
       <c r="B46" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>128458394</v>
       </c>
       <c r="B47" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>128458391</v>
       </c>
       <c r="B48" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>128472156</v>
       </c>
       <c r="B49" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>128472174</v>
       </c>
       <c r="B51" t="n">
-        <v>98496</v>
+        <v>98502</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>128472149</v>
       </c>
       <c r="B52" t="n">
-        <v>92155</v>
+        <v>92161</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>128472158</v>
       </c>
       <c r="B53" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>128472148</v>
       </c>
       <c r="B57" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>128472157</v>
       </c>
       <c r="B60" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -1725,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128458684</v>
+        <v>128458361</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>679669</v>
+        <v>679603</v>
       </c>
       <c r="R12" t="n">
-        <v>7118266</v>
+        <v>7118423</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,6 +1796,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,45 +1827,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128458390</v>
+        <v>128458666</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>98585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679650</v>
+        <v>679677</v>
       </c>
       <c r="R13" t="n">
-        <v>7118244</v>
+        <v>7118227</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1895,12 +1912,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Blomställning</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1919,10 +1942,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128458361</v>
+        <v>128458684</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1930,21 +1953,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1977,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>679603</v>
+        <v>679669</v>
       </c>
       <c r="R14" t="n">
-        <v>7118423</v>
+        <v>7118266</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1990,11 +2013,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2021,10 +2039,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128458345</v>
+        <v>128458390</v>
       </c>
       <c r="B15" t="n">
-        <v>57849</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,21 +2050,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>679629</v>
+        <v>679650</v>
       </c>
       <c r="R15" t="n">
-        <v>7118222</v>
+        <v>7118244</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,57 +2136,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128458666</v>
+        <v>128458345</v>
       </c>
       <c r="B16" t="n">
-        <v>98585</v>
+        <v>57849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>679677</v>
+        <v>679629</v>
       </c>
       <c r="R16" t="n">
-        <v>7118227</v>
+        <v>7118222</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,18 +2209,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Blomställning</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128458343</v>
+        <v>128458651</v>
       </c>
       <c r="B4" t="n">
-        <v>56880</v>
+        <v>97462</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>679724</v>
+        <v>679660</v>
       </c>
       <c r="R4" t="n">
-        <v>7118278</v>
+        <v>7118198</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128458651</v>
+        <v>128458343</v>
       </c>
       <c r="B5" t="n">
-        <v>97460</v>
+        <v>56880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>679660</v>
+        <v>679724</v>
       </c>
       <c r="R5" t="n">
-        <v>7118198</v>
+        <v>7118278</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1327,7 +1327,7 @@
         <v>128458393</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>128458380</v>
       </c>
       <c r="B11" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1827,57 +1827,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128458666</v>
+        <v>128458345</v>
       </c>
       <c r="B13" t="n">
-        <v>98585</v>
+        <v>57849</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679677</v>
+        <v>679629</v>
       </c>
       <c r="R13" t="n">
-        <v>7118227</v>
+        <v>7118222</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,18 +1900,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Blomställning</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1945,7 +1927,7 @@
         <v>128458684</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,7 +2024,7 @@
         <v>128458390</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,45 +2118,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128458345</v>
+        <v>128458666</v>
       </c>
       <c r="B16" t="n">
-        <v>57849</v>
+        <v>98588</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>679629</v>
+        <v>679677</v>
       </c>
       <c r="R16" t="n">
-        <v>7118222</v>
+        <v>7118227</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,12 +2203,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Blomställning</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2330,32 +2330,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128458392</v>
+        <v>128458339</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>91431</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>679587</v>
+        <v>679682</v>
       </c>
       <c r="R18" t="n">
-        <v>7118403</v>
+        <v>7118294</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2420,17 +2420,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Felix Gustafsson</t>
+          <t>Felix Gustafsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128458400</v>
+        <v>128458392</v>
       </c>
       <c r="B19" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>679599</v>
+        <v>679587</v>
       </c>
       <c r="R19" t="n">
-        <v>7118424</v>
+        <v>7118403</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2498,11 +2498,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2626,32 +2621,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128458339</v>
+        <v>128458400</v>
       </c>
       <c r="B21" t="n">
-        <v>91429</v>
+        <v>57689</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2661,10 +2656,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>679682</v>
+        <v>679599</v>
       </c>
       <c r="R21" t="n">
-        <v>7118294</v>
+        <v>7118424</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2697,6 +2692,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2726,7 +2726,7 @@
         <v>128458690</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2820,10 +2820,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128458396</v>
+        <v>128458383</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>679612</v>
+        <v>679564</v>
       </c>
       <c r="R23" t="n">
-        <v>7118334</v>
+        <v>7118347</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,12 +2893,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2917,10 +2923,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128458383</v>
+        <v>128458396</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2952,10 +2958,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>679564</v>
+        <v>679612</v>
       </c>
       <c r="R24" t="n">
-        <v>7118347</v>
+        <v>7118334</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2990,18 +2996,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3023,7 +3023,7 @@
         <v>128458688</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>128458686</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>128458667</v>
       </c>
       <c r="B28" t="n">
-        <v>75158</v>
+        <v>75160</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>128458363</v>
       </c>
       <c r="B30" t="n">
-        <v>80220</v>
+        <v>80222</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>128458397</v>
       </c>
       <c r="B31" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>128458683</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>128458395</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4000,10 +4000,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458689</v>
+        <v>128458669</v>
       </c>
       <c r="B35" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>679651</v>
+        <v>679615</v>
       </c>
       <c r="R35" t="n">
-        <v>7118207</v>
+        <v>7118231</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4073,12 +4073,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4097,10 +4103,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458341</v>
+        <v>128458650</v>
       </c>
       <c r="B36" t="n">
-        <v>79706</v>
+        <v>57689</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4108,21 +4114,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4132,10 +4138,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679625</v>
+        <v>679651</v>
       </c>
       <c r="R36" t="n">
-        <v>7118333</v>
+        <v>7118217</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4168,6 +4174,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4194,10 +4205,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458669</v>
+        <v>128458689</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4229,10 +4240,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679615</v>
+        <v>679651</v>
       </c>
       <c r="R37" t="n">
-        <v>7118231</v>
+        <v>7118207</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4267,18 +4278,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4297,10 +4302,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128458650</v>
+        <v>128458341</v>
       </c>
       <c r="B38" t="n">
-        <v>57689</v>
+        <v>79708</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4308,21 +4313,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4332,10 +4337,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679651</v>
+        <v>679625</v>
       </c>
       <c r="R38" t="n">
-        <v>7118217</v>
+        <v>7118333</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4368,11 +4373,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4504,7 +4504,7 @@
         <v>128458338</v>
       </c>
       <c r="B40" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Felix Gustafsson</t>
+          <t>Felix Gustafsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128458685</v>
+        <v>128458398</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>679565</v>
+        <v>679689</v>
       </c>
       <c r="R41" t="n">
-        <v>7118208</v>
+        <v>7118284</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4695,10 +4695,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128458398</v>
+        <v>128458685</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679689</v>
+        <v>679565</v>
       </c>
       <c r="R42" t="n">
-        <v>7118284</v>
+        <v>7118208</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5101,7 +5101,7 @@
         <v>128458682</v>
       </c>
       <c r="B46" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>128458394</v>
       </c>
       <c r="B47" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>128458391</v>
       </c>
       <c r="B48" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>128472156</v>
       </c>
       <c r="B49" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>128472170</v>
       </c>
       <c r="B50" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>128472174</v>
       </c>
       <c r="B51" t="n">
-        <v>98502</v>
+        <v>98505</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>128472149</v>
       </c>
       <c r="B52" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>128472158</v>
       </c>
       <c r="B53" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>128472169</v>
       </c>
       <c r="B54" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>128472148</v>
       </c>
       <c r="B57" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>128472172</v>
       </c>
       <c r="B58" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>128472159</v>
       </c>
       <c r="B59" t="n">
-        <v>80220</v>
+        <v>80222</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>128472157</v>
       </c>
       <c r="B60" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>128472168</v>
       </c>
       <c r="B62" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>128472167</v>
       </c>
       <c r="B63" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>128501348</v>
       </c>
       <c r="B64" t="n">
-        <v>75175</v>
+        <v>75177</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128458651</v>
+        <v>128458343</v>
       </c>
       <c r="B4" t="n">
-        <v>97462</v>
+        <v>56880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>679660</v>
+        <v>679724</v>
       </c>
       <c r="R4" t="n">
-        <v>7118198</v>
+        <v>7118278</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128458343</v>
+        <v>128458651</v>
       </c>
       <c r="B5" t="n">
-        <v>56880</v>
+        <v>97462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>679724</v>
+        <v>679660</v>
       </c>
       <c r="R5" t="n">
-        <v>7118278</v>
+        <v>7118198</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1725,45 +1725,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128458361</v>
+        <v>128458666</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>98591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>679603</v>
+        <v>679677</v>
       </c>
       <c r="R12" t="n">
-        <v>7118423</v>
+        <v>7118227</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1812,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Blomställning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1809,6 +1821,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1827,10 +1840,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128458345</v>
+        <v>128458684</v>
       </c>
       <c r="B13" t="n">
-        <v>57849</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,21 +1851,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1875,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679629</v>
+        <v>679669</v>
       </c>
       <c r="R13" t="n">
-        <v>7118222</v>
+        <v>7118266</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,7 +1937,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128458684</v>
+        <v>128458390</v>
       </c>
       <c r="B14" t="n">
         <v>79089</v>
@@ -1959,10 +1972,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>679669</v>
+        <v>679650</v>
       </c>
       <c r="R14" t="n">
-        <v>7118266</v>
+        <v>7118244</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,10 +2034,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128458390</v>
+        <v>128458361</v>
       </c>
       <c r="B15" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,21 +2045,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2069,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>679650</v>
+        <v>679603</v>
       </c>
       <c r="R15" t="n">
-        <v>7118244</v>
+        <v>7118423</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2092,6 +2105,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2118,57 +2136,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128458666</v>
+        <v>128458345</v>
       </c>
       <c r="B16" t="n">
-        <v>98588</v>
+        <v>57849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>679677</v>
+        <v>679629</v>
       </c>
       <c r="R16" t="n">
-        <v>7118227</v>
+        <v>7118222</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,18 +2209,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Blomställning</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2820,7 +2820,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128458383</v>
+        <v>128458396</v>
       </c>
       <c r="B23" t="n">
         <v>79089</v>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>679564</v>
+        <v>679612</v>
       </c>
       <c r="R23" t="n">
-        <v>7118347</v>
+        <v>7118334</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,18 +2893,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2923,7 +2917,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128458396</v>
+        <v>128458383</v>
       </c>
       <c r="B24" t="n">
         <v>79089</v>
@@ -2958,10 +2952,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>679612</v>
+        <v>679564</v>
       </c>
       <c r="R24" t="n">
-        <v>7118334</v>
+        <v>7118347</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2996,12 +2990,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3510,32 +3510,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128458363</v>
+        <v>128458397</v>
       </c>
       <c r="B30" t="n">
-        <v>80222</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>679619</v>
+        <v>679666</v>
       </c>
       <c r="R30" t="n">
-        <v>7118451</v>
+        <v>7118288</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3607,7 +3607,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128458397</v>
+        <v>128458683</v>
       </c>
       <c r="B31" t="n">
         <v>79089</v>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>679666</v>
+        <v>679678</v>
       </c>
       <c r="R31" t="n">
-        <v>7118288</v>
+        <v>7118309</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3704,32 +3704,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128458683</v>
+        <v>128458363</v>
       </c>
       <c r="B32" t="n">
-        <v>79089</v>
+        <v>80222</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>679678</v>
+        <v>679619</v>
       </c>
       <c r="R32" t="n">
-        <v>7118309</v>
+        <v>7118451</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458669</v>
+        <v>128458689</v>
       </c>
       <c r="B35" t="n">
         <v>79089</v>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>679615</v>
+        <v>679651</v>
       </c>
       <c r="R35" t="n">
-        <v>7118231</v>
+        <v>7118207</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4073,18 +4073,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4103,10 +4097,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458650</v>
+        <v>128458341</v>
       </c>
       <c r="B36" t="n">
-        <v>57689</v>
+        <v>79708</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4114,21 +4108,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4138,10 +4132,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679651</v>
+        <v>679625</v>
       </c>
       <c r="R36" t="n">
-        <v>7118217</v>
+        <v>7118333</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4174,11 +4168,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4205,7 +4194,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458689</v>
+        <v>128458669</v>
       </c>
       <c r="B37" t="n">
         <v>79089</v>
@@ -4240,10 +4229,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679651</v>
+        <v>679615</v>
       </c>
       <c r="R37" t="n">
-        <v>7118207</v>
+        <v>7118231</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4278,12 +4267,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4302,10 +4297,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128458341</v>
+        <v>128458650</v>
       </c>
       <c r="B38" t="n">
-        <v>79708</v>
+        <v>57689</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4313,21 +4308,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4337,10 +4332,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679625</v>
+        <v>679651</v>
       </c>
       <c r="R38" t="n">
-        <v>7118333</v>
+        <v>7118217</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4373,6 +4368,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4501,32 +4501,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128458338</v>
+        <v>128458685</v>
       </c>
       <c r="B40" t="n">
-        <v>91431</v>
+        <v>79089</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>679591</v>
+        <v>679565</v>
       </c>
       <c r="R40" t="n">
-        <v>7118426</v>
+        <v>7118208</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4695,32 +4695,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128458685</v>
+        <v>128458665</v>
       </c>
       <c r="B42" t="n">
-        <v>79089</v>
+        <v>58059</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679565</v>
+        <v>679618</v>
       </c>
       <c r="R42" t="n">
-        <v>7118208</v>
+        <v>7118186</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4766,6 +4766,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>läte</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4792,32 +4797,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128458354</v>
+        <v>128458338</v>
       </c>
       <c r="B43" t="n">
-        <v>57689</v>
+        <v>91431</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4827,10 +4832,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>679621</v>
+        <v>679591</v>
       </c>
       <c r="R43" t="n">
-        <v>7118296</v>
+        <v>7118426</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4863,11 +4868,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4894,7 +4894,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128458359</v>
+        <v>128458354</v>
       </c>
       <c r="B44" t="n">
         <v>57689</v>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>679602</v>
+        <v>679621</v>
       </c>
       <c r="R44" t="n">
-        <v>7118340</v>
+        <v>7118296</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4996,27 +4996,27 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128458665</v>
+        <v>128458359</v>
       </c>
       <c r="B45" t="n">
-        <v>58059</v>
+        <v>57689</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5031,10 +5031,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>679618</v>
+        <v>679602</v>
       </c>
       <c r="R45" t="n">
-        <v>7118186</v>
+        <v>7118340</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>läte</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5586,7 +5586,7 @@
         <v>128472174</v>
       </c>
       <c r="B51" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128458646</v>
+        <v>128458639</v>
       </c>
       <c r="B6" t="n">
-        <v>57686</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,34 +1124,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>679701</v>
+        <v>679614</v>
       </c>
       <c r="R6" t="n">
-        <v>7118347</v>
+        <v>7118176</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,11 +1196,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre hack på låga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128458639</v>
+        <v>128458646</v>
       </c>
       <c r="B7" t="n">
-        <v>57849</v>
+        <v>57686</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,46 +1233,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>679614</v>
+        <v>679701</v>
       </c>
       <c r="R7" t="n">
-        <v>7118176</v>
+        <v>7118347</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,6 +1293,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre hack på låga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128458380</v>
+        <v>128458684</v>
       </c>
       <c r="B11" t="n">
-        <v>91484</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>679630</v>
+        <v>679669</v>
       </c>
       <c r="R11" t="n">
-        <v>7118401</v>
+        <v>7118266</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,57 +1725,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128458666</v>
+        <v>128458390</v>
       </c>
       <c r="B12" t="n">
-        <v>98591</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>679677</v>
+        <v>679650</v>
       </c>
       <c r="R12" t="n">
-        <v>7118227</v>
+        <v>7118244</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,18 +1798,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Blomställning</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1840,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128458684</v>
+        <v>128458380</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>91484</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1875,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679669</v>
+        <v>679630</v>
       </c>
       <c r="R13" t="n">
-        <v>7118266</v>
+        <v>7118401</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128458390</v>
+        <v>128458361</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1972,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>679650</v>
+        <v>679603</v>
       </c>
       <c r="R14" t="n">
-        <v>7118244</v>
+        <v>7118423</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2008,6 +1990,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2034,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128458361</v>
+        <v>128458345</v>
       </c>
       <c r="B15" t="n">
-        <v>57689</v>
+        <v>57849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2045,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2069,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>679603</v>
+        <v>679629</v>
       </c>
       <c r="R15" t="n">
-        <v>7118423</v>
+        <v>7118222</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,11 +2092,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2136,45 +2118,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128458345</v>
+        <v>128458666</v>
       </c>
       <c r="B16" t="n">
-        <v>57849</v>
+        <v>98591</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>679629</v>
+        <v>679677</v>
       </c>
       <c r="R16" t="n">
-        <v>7118222</v>
+        <v>7118227</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,12 +2203,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Blomställning</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2330,32 +2330,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128458339</v>
+        <v>128458392</v>
       </c>
       <c r="B18" t="n">
-        <v>91431</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>679682</v>
+        <v>679587</v>
       </c>
       <c r="R18" t="n">
-        <v>7118294</v>
+        <v>7118403</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,32 +2427,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128458392</v>
+        <v>128458339</v>
       </c>
       <c r="B19" t="n">
-        <v>79089</v>
+        <v>91431</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>679587</v>
+        <v>679682</v>
       </c>
       <c r="R19" t="n">
-        <v>7118403</v>
+        <v>7118294</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128458352</v>
+        <v>128458400</v>
       </c>
       <c r="B20" t="n">
-        <v>57686</v>
+        <v>57689</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,16 +2535,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>679621</v>
+        <v>679599</v>
       </c>
       <c r="R20" t="n">
-        <v>7118452</v>
+        <v>7118424</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2595,6 +2595,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2621,10 +2626,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128458400</v>
+        <v>128458352</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>57686</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2632,16 +2637,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2656,10 +2661,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>679599</v>
+        <v>679621</v>
       </c>
       <c r="R21" t="n">
-        <v>7118424</v>
+        <v>7118452</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2692,11 +2697,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4000,10 +4000,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458689</v>
+        <v>128458650</v>
       </c>
       <c r="B35" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4011,21 +4011,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4038,7 +4038,7 @@
         <v>679651</v>
       </c>
       <c r="R35" t="n">
-        <v>7118207</v>
+        <v>7118217</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4071,6 +4071,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4097,10 +4102,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458341</v>
+        <v>128458689</v>
       </c>
       <c r="B36" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4108,21 +4113,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4132,10 +4137,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679625</v>
+        <v>679651</v>
       </c>
       <c r="R36" t="n">
-        <v>7118333</v>
+        <v>7118207</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,10 +4199,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458669</v>
+        <v>128458341</v>
       </c>
       <c r="B37" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4205,21 +4210,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4229,10 +4234,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679615</v>
+        <v>679625</v>
       </c>
       <c r="R37" t="n">
-        <v>7118231</v>
+        <v>7118333</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4267,18 +4272,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4297,10 +4296,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128458650</v>
+        <v>128458669</v>
       </c>
       <c r="B38" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4308,21 +4307,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4332,10 +4331,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679651</v>
+        <v>679615</v>
       </c>
       <c r="R38" t="n">
-        <v>7118217</v>
+        <v>7118231</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4372,7 +4371,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4381,6 +4380,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4695,10 +4695,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128458665</v>
+        <v>128458338</v>
       </c>
       <c r="B42" t="n">
-        <v>58059</v>
+        <v>91431</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4706,21 +4706,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679618</v>
+        <v>679591</v>
       </c>
       <c r="R42" t="n">
-        <v>7118186</v>
+        <v>7118426</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4766,11 +4766,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>läte</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4797,10 +4792,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128458338</v>
+        <v>128458665</v>
       </c>
       <c r="B43" t="n">
-        <v>91431</v>
+        <v>58059</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4808,21 +4803,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>103015</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4832,10 +4827,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>679591</v>
+        <v>679618</v>
       </c>
       <c r="R43" t="n">
-        <v>7118426</v>
+        <v>7118186</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4868,6 +4863,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>läte</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>128458651</v>
       </c>
       <c r="B5" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128458639</v>
+        <v>128458646</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>57686</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,46 +1124,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>679614</v>
+        <v>679701</v>
       </c>
       <c r="R6" t="n">
-        <v>7118176</v>
+        <v>7118347</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,6 +1184,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre hack på låga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128458646</v>
+        <v>128458639</v>
       </c>
       <c r="B7" t="n">
-        <v>57686</v>
+        <v>57849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1233,34 +1226,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>679701</v>
+        <v>679614</v>
       </c>
       <c r="R7" t="n">
-        <v>7118347</v>
+        <v>7118176</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,11 +1298,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre hack på låga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128458380</v>
+        <v>128458361</v>
       </c>
       <c r="B13" t="n">
-        <v>91484</v>
+        <v>57689</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679630</v>
+        <v>679603</v>
       </c>
       <c r="R13" t="n">
-        <v>7118401</v>
+        <v>7118423</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1893,6 +1893,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1919,45 +1924,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128458361</v>
+        <v>128458666</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
+        <v>98592</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>679603</v>
+        <v>679677</v>
       </c>
       <c r="R14" t="n">
-        <v>7118423</v>
+        <v>7118227</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,7 +2011,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Blomställning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2003,6 +2020,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2021,10 +2039,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128458345</v>
+        <v>128458380</v>
       </c>
       <c r="B15" t="n">
-        <v>57849</v>
+        <v>91485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,21 +2050,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>679629</v>
+        <v>679630</v>
       </c>
       <c r="R15" t="n">
-        <v>7118222</v>
+        <v>7118401</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,57 +2136,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128458666</v>
+        <v>128458345</v>
       </c>
       <c r="B16" t="n">
-        <v>98591</v>
+        <v>57849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>679677</v>
+        <v>679629</v>
       </c>
       <c r="R16" t="n">
-        <v>7118227</v>
+        <v>7118222</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,18 +2209,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Blomställning</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2330,10 +2330,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128458392</v>
+        <v>128458400</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2341,21 +2341,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>679587</v>
+        <v>679599</v>
       </c>
       <c r="R18" t="n">
-        <v>7118403</v>
+        <v>7118424</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2401,6 +2401,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2427,32 +2432,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128458339</v>
+        <v>128458392</v>
       </c>
       <c r="B19" t="n">
-        <v>91431</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2462,10 +2467,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>679682</v>
+        <v>679587</v>
       </c>
       <c r="R19" t="n">
-        <v>7118294</v>
+        <v>7118403</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2524,32 +2529,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128458400</v>
+        <v>128458339</v>
       </c>
       <c r="B20" t="n">
-        <v>57689</v>
+        <v>91432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2559,10 +2564,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>679599</v>
+        <v>679682</v>
       </c>
       <c r="R20" t="n">
-        <v>7118424</v>
+        <v>7118294</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2595,11 +2600,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3020,10 +3020,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128458688</v>
+        <v>128458360</v>
       </c>
       <c r="B25" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3031,21 +3031,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>679619</v>
+        <v>679584</v>
       </c>
       <c r="R25" t="n">
-        <v>7118185</v>
+        <v>7118426</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3091,6 +3091,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3117,7 +3122,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128458686</v>
+        <v>128458688</v>
       </c>
       <c r="B26" t="n">
         <v>79089</v>
@@ -3152,10 +3157,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>679592</v>
+        <v>679619</v>
       </c>
       <c r="R26" t="n">
-        <v>7118161</v>
+        <v>7118185</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3214,10 +3219,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128458360</v>
+        <v>128458686</v>
       </c>
       <c r="B27" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3225,21 +3230,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3249,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>679584</v>
+        <v>679592</v>
       </c>
       <c r="R27" t="n">
-        <v>7118426</v>
+        <v>7118161</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3285,11 +3290,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3801,10 +3801,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128458395</v>
+        <v>128458649</v>
       </c>
       <c r="B33" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3812,21 +3812,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>679643</v>
+        <v>679607</v>
       </c>
       <c r="R33" t="n">
-        <v>7118369</v>
+        <v>7118183</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3872,6 +3872,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3898,10 +3903,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128458649</v>
+        <v>128458395</v>
       </c>
       <c r="B34" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3909,21 +3914,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3933,10 +3938,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>679607</v>
+        <v>679643</v>
       </c>
       <c r="R34" t="n">
-        <v>7118183</v>
+        <v>7118369</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3969,11 +3974,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4000,10 +4000,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458650</v>
+        <v>128458341</v>
       </c>
       <c r="B35" t="n">
-        <v>57689</v>
+        <v>79708</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4011,21 +4011,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>679651</v>
+        <v>679625</v>
       </c>
       <c r="R35" t="n">
-        <v>7118217</v>
+        <v>7118333</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4071,11 +4071,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4102,10 +4097,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458689</v>
+        <v>128458650</v>
       </c>
       <c r="B36" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4113,21 +4108,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4140,7 +4135,7 @@
         <v>679651</v>
       </c>
       <c r="R36" t="n">
-        <v>7118207</v>
+        <v>7118217</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4173,6 +4168,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4199,10 +4199,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458341</v>
+        <v>128458689</v>
       </c>
       <c r="B37" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4210,21 +4210,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679625</v>
+        <v>679651</v>
       </c>
       <c r="R37" t="n">
-        <v>7118333</v>
+        <v>7118207</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4698,7 +4698,7 @@
         <v>128458338</v>
       </c>
       <c r="B42" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4792,27 +4792,27 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128458665</v>
+        <v>128458354</v>
       </c>
       <c r="B43" t="n">
-        <v>58059</v>
+        <v>57689</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>679618</v>
+        <v>679621</v>
       </c>
       <c r="R43" t="n">
-        <v>7118186</v>
+        <v>7118296</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>läte</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4894,7 +4894,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128458354</v>
+        <v>128458359</v>
       </c>
       <c r="B44" t="n">
         <v>57689</v>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>679621</v>
+        <v>679602</v>
       </c>
       <c r="R44" t="n">
-        <v>7118296</v>
+        <v>7118340</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4996,27 +4996,27 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128458359</v>
+        <v>128458665</v>
       </c>
       <c r="B45" t="n">
-        <v>57689</v>
+        <v>58059</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5031,10 +5031,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>679602</v>
+        <v>679618</v>
       </c>
       <c r="R45" t="n">
-        <v>7118340</v>
+        <v>7118186</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>läte</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5392,7 +5392,7 @@
         <v>128472156</v>
       </c>
       <c r="B49" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>128472174</v>
       </c>
       <c r="B51" t="n">
-        <v>98508</v>
+        <v>98509</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>128472149</v>
       </c>
       <c r="B52" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>128472158</v>
       </c>
       <c r="B53" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>128472148</v>
       </c>
       <c r="B57" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>128472157</v>
       </c>
       <c r="B60" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -2330,10 +2330,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128458400</v>
+        <v>128458392</v>
       </c>
       <c r="B18" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2341,21 +2341,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>679599</v>
+        <v>679587</v>
       </c>
       <c r="R18" t="n">
-        <v>7118424</v>
+        <v>7118403</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2401,11 +2401,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2432,32 +2427,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128458392</v>
+        <v>128458339</v>
       </c>
       <c r="B19" t="n">
-        <v>79089</v>
+        <v>91432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2467,10 +2462,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>679587</v>
+        <v>679682</v>
       </c>
       <c r="R19" t="n">
-        <v>7118403</v>
+        <v>7118294</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2529,32 +2524,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128458339</v>
+        <v>128458352</v>
       </c>
       <c r="B20" t="n">
-        <v>91432</v>
+        <v>57686</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2564,10 +2559,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>679682</v>
+        <v>679621</v>
       </c>
       <c r="R20" t="n">
-        <v>7118294</v>
+        <v>7118452</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2626,10 +2621,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128458352</v>
+        <v>128458400</v>
       </c>
       <c r="B21" t="n">
-        <v>57686</v>
+        <v>57689</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2637,16 +2632,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2661,10 +2656,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>679621</v>
+        <v>679599</v>
       </c>
       <c r="R21" t="n">
-        <v>7118452</v>
+        <v>7118424</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2697,6 +2692,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3020,10 +3020,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128458360</v>
+        <v>128458688</v>
       </c>
       <c r="B25" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3031,21 +3031,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>679584</v>
+        <v>679619</v>
       </c>
       <c r="R25" t="n">
-        <v>7118426</v>
+        <v>7118185</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3091,11 +3091,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3122,10 +3117,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128458688</v>
+        <v>128458360</v>
       </c>
       <c r="B26" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,21 +3128,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3157,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>679619</v>
+        <v>679584</v>
       </c>
       <c r="R26" t="n">
-        <v>7118185</v>
+        <v>7118426</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3193,6 +3188,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3510,32 +3510,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128458397</v>
+        <v>128458363</v>
       </c>
       <c r="B30" t="n">
-        <v>79089</v>
+        <v>80222</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>679666</v>
+        <v>679619</v>
       </c>
       <c r="R30" t="n">
-        <v>7118288</v>
+        <v>7118451</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3607,7 +3607,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128458683</v>
+        <v>128458397</v>
       </c>
       <c r="B31" t="n">
         <v>79089</v>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>679678</v>
+        <v>679666</v>
       </c>
       <c r="R31" t="n">
-        <v>7118309</v>
+        <v>7118288</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3704,32 +3704,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128458363</v>
+        <v>128458683</v>
       </c>
       <c r="B32" t="n">
-        <v>80222</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>679619</v>
+        <v>679678</v>
       </c>
       <c r="R32" t="n">
-        <v>7118451</v>
+        <v>7118309</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -5392,7 +5392,7 @@
         <v>128472156</v>
       </c>
       <c r="B49" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>128472170</v>
       </c>
       <c r="B50" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>128472174</v>
       </c>
       <c r="B51" t="n">
-        <v>98509</v>
+        <v>98536</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>128472149</v>
       </c>
       <c r="B52" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>128472158</v>
       </c>
       <c r="B53" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>128472169</v>
       </c>
       <c r="B54" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>128472165</v>
       </c>
       <c r="B55" t="n">
-        <v>57793</v>
+        <v>57820</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>128472166</v>
       </c>
       <c r="B56" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>128472148</v>
       </c>
       <c r="B57" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>128472172</v>
       </c>
       <c r="B58" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>128472159</v>
       </c>
       <c r="B59" t="n">
-        <v>80222</v>
+        <v>80249</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>128472157</v>
       </c>
       <c r="B60" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>128472171</v>
       </c>
       <c r="B61" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>128472168</v>
       </c>
       <c r="B62" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>128472167</v>
       </c>
       <c r="B63" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>128501348</v>
       </c>
       <c r="B64" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128458343</v>
+        <v>128458651</v>
       </c>
       <c r="B4" t="n">
-        <v>56880</v>
+        <v>97490</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>679724</v>
+        <v>679660</v>
       </c>
       <c r="R4" t="n">
-        <v>7118278</v>
+        <v>7118198</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128458651</v>
+        <v>128458343</v>
       </c>
       <c r="B5" t="n">
-        <v>97463</v>
+        <v>56907</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>679660</v>
+        <v>679724</v>
       </c>
       <c r="R5" t="n">
-        <v>7118198</v>
+        <v>7118278</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,7 +1116,7 @@
         <v>128458646</v>
       </c>
       <c r="B6" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128458639</v>
       </c>
       <c r="B7" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>128458393</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>128458355</v>
       </c>
       <c r="B9" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>128458379</v>
       </c>
       <c r="B10" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128458684</v>
+        <v>128458380</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>91512</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>679669</v>
+        <v>679630</v>
       </c>
       <c r="R11" t="n">
-        <v>7118266</v>
+        <v>7118401</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128458390</v>
+        <v>128458684</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>679650</v>
+        <v>679669</v>
       </c>
       <c r="R12" t="n">
-        <v>7118244</v>
+        <v>7118266</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128458361</v>
+        <v>128458390</v>
       </c>
       <c r="B13" t="n">
-        <v>57689</v>
+        <v>79116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679603</v>
+        <v>679650</v>
       </c>
       <c r="R13" t="n">
-        <v>7118423</v>
+        <v>7118244</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1893,11 +1893,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,57 +1919,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128458666</v>
+        <v>128458345</v>
       </c>
       <c r="B14" t="n">
-        <v>98592</v>
+        <v>57876</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>679677</v>
+        <v>679629</v>
       </c>
       <c r="R14" t="n">
-        <v>7118227</v>
+        <v>7118222</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2009,18 +1992,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Blomställning</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2039,45 +2016,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128458380</v>
+        <v>128458666</v>
       </c>
       <c r="B15" t="n">
-        <v>91485</v>
+        <v>98619</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>679630</v>
+        <v>679677</v>
       </c>
       <c r="R15" t="n">
-        <v>7118401</v>
+        <v>7118227</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,12 +2101,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Blomställning</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2136,10 +2131,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128458345</v>
+        <v>128458361</v>
       </c>
       <c r="B16" t="n">
-        <v>57849</v>
+        <v>57716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2147,21 +2142,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,10 +2166,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>679629</v>
+        <v>679603</v>
       </c>
       <c r="R16" t="n">
-        <v>7118222</v>
+        <v>7118423</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2207,6 +2202,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2236,7 +2236,7 @@
         <v>128458348</v>
       </c>
       <c r="B17" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>128458392</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,32 +2427,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128458339</v>
+        <v>128458400</v>
       </c>
       <c r="B19" t="n">
-        <v>91432</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>679682</v>
+        <v>679599</v>
       </c>
       <c r="R19" t="n">
-        <v>7118294</v>
+        <v>7118424</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2498,6 +2498,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2524,32 +2529,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128458352</v>
+        <v>128458339</v>
       </c>
       <c r="B20" t="n">
-        <v>57686</v>
+        <v>91459</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2559,10 +2564,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>679621</v>
+        <v>679682</v>
       </c>
       <c r="R20" t="n">
-        <v>7118452</v>
+        <v>7118294</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2621,10 +2626,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128458400</v>
+        <v>128458352</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>57713</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2632,16 +2637,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2656,10 +2661,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>679599</v>
+        <v>679621</v>
       </c>
       <c r="R21" t="n">
-        <v>7118424</v>
+        <v>7118452</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2692,11 +2697,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2726,7 +2726,7 @@
         <v>128458690</v>
       </c>
       <c r="B22" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2820,10 +2820,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128458396</v>
+        <v>128458383</v>
       </c>
       <c r="B23" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>679612</v>
+        <v>679564</v>
       </c>
       <c r="R23" t="n">
-        <v>7118334</v>
+        <v>7118347</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,12 +2893,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2917,10 +2923,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128458383</v>
+        <v>128458396</v>
       </c>
       <c r="B24" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2952,10 +2958,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>679564</v>
+        <v>679612</v>
       </c>
       <c r="R24" t="n">
-        <v>7118347</v>
+        <v>7118334</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2990,18 +2996,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3023,7 +3023,7 @@
         <v>128458688</v>
       </c>
       <c r="B25" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3117,10 +3117,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128458360</v>
+        <v>128458686</v>
       </c>
       <c r="B26" t="n">
-        <v>57689</v>
+        <v>79116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3128,21 +3128,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>679584</v>
+        <v>679592</v>
       </c>
       <c r="R26" t="n">
-        <v>7118426</v>
+        <v>7118161</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3188,11 +3188,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3219,10 +3214,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128458686</v>
+        <v>128458360</v>
       </c>
       <c r="B27" t="n">
-        <v>79089</v>
+        <v>57716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3230,21 +3225,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3254,10 +3249,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>679592</v>
+        <v>679584</v>
       </c>
       <c r="R27" t="n">
-        <v>7118161</v>
+        <v>7118426</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3290,6 +3285,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3316,32 +3316,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128458667</v>
+        <v>128458347</v>
       </c>
       <c r="B28" t="n">
-        <v>75160</v>
+        <v>57876</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6439</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>679624</v>
+        <v>679582</v>
       </c>
       <c r="R28" t="n">
-        <v>7118176</v>
+        <v>7118432</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3413,32 +3413,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128458347</v>
+        <v>128458667</v>
       </c>
       <c r="B29" t="n">
-        <v>57849</v>
+        <v>75187</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6439</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>679582</v>
+        <v>679624</v>
       </c>
       <c r="R29" t="n">
-        <v>7118432</v>
+        <v>7118176</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3510,32 +3510,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128458363</v>
+        <v>128458397</v>
       </c>
       <c r="B30" t="n">
-        <v>80222</v>
+        <v>79116</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>679619</v>
+        <v>679666</v>
       </c>
       <c r="R30" t="n">
-        <v>7118451</v>
+        <v>7118288</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3607,10 +3607,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128458397</v>
+        <v>128458683</v>
       </c>
       <c r="B31" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>679666</v>
+        <v>679678</v>
       </c>
       <c r="R31" t="n">
-        <v>7118288</v>
+        <v>7118309</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3704,32 +3704,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128458683</v>
+        <v>128458363</v>
       </c>
       <c r="B32" t="n">
-        <v>79089</v>
+        <v>80249</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>679678</v>
+        <v>679619</v>
       </c>
       <c r="R32" t="n">
-        <v>7118309</v>
+        <v>7118451</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3804,7 +3804,7 @@
         <v>128458649</v>
       </c>
       <c r="B33" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>128458395</v>
       </c>
       <c r="B34" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4000,10 +4000,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458341</v>
+        <v>128458689</v>
       </c>
       <c r="B35" t="n">
-        <v>79708</v>
+        <v>79116</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4011,21 +4011,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>679625</v>
+        <v>679651</v>
       </c>
       <c r="R35" t="n">
-        <v>7118333</v>
+        <v>7118207</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4097,10 +4097,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458650</v>
+        <v>128458669</v>
       </c>
       <c r="B36" t="n">
-        <v>57689</v>
+        <v>79116</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679651</v>
+        <v>679615</v>
       </c>
       <c r="R36" t="n">
-        <v>7118217</v>
+        <v>7118231</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4181,6 +4181,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4199,10 +4200,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458689</v>
+        <v>128458341</v>
       </c>
       <c r="B37" t="n">
-        <v>79089</v>
+        <v>79735</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4210,21 +4211,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4234,10 +4235,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679651</v>
+        <v>679625</v>
       </c>
       <c r="R37" t="n">
-        <v>7118207</v>
+        <v>7118333</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4296,10 +4297,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128458669</v>
+        <v>128458650</v>
       </c>
       <c r="B38" t="n">
-        <v>79089</v>
+        <v>57716</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4307,21 +4308,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4331,10 +4332,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679615</v>
+        <v>679651</v>
       </c>
       <c r="R38" t="n">
-        <v>7118231</v>
+        <v>7118217</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4371,7 +4372,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Med apotecier</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4380,7 +4381,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4402,7 +4402,7 @@
         <v>128458357</v>
       </c>
       <c r="B39" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>128458685</v>
       </c>
       <c r="B40" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4598,32 +4598,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128458398</v>
+        <v>128458338</v>
       </c>
       <c r="B41" t="n">
-        <v>79089</v>
+        <v>91459</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>679689</v>
+        <v>679591</v>
       </c>
       <c r="R41" t="n">
-        <v>7118284</v>
+        <v>7118426</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4695,32 +4695,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128458338</v>
+        <v>128458398</v>
       </c>
       <c r="B42" t="n">
-        <v>91432</v>
+        <v>79116</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679591</v>
+        <v>679689</v>
       </c>
       <c r="R42" t="n">
-        <v>7118426</v>
+        <v>7118284</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4795,7 +4795,7 @@
         <v>128458354</v>
       </c>
       <c r="B43" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>128458359</v>
       </c>
       <c r="B44" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>128458665</v>
       </c>
       <c r="B45" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>128458682</v>
       </c>
       <c r="B46" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>128458394</v>
       </c>
       <c r="B47" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>128458391</v>
       </c>
       <c r="B48" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128458651</v>
+        <v>128458343</v>
       </c>
       <c r="B4" t="n">
-        <v>97490</v>
+        <v>56907</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>679660</v>
+        <v>679724</v>
       </c>
       <c r="R4" t="n">
-        <v>7118198</v>
+        <v>7118278</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128458343</v>
+        <v>128458651</v>
       </c>
       <c r="B5" t="n">
-        <v>56907</v>
+        <v>97490</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>679724</v>
+        <v>679660</v>
       </c>
       <c r="R5" t="n">
-        <v>7118278</v>
+        <v>7118198</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128458646</v>
+        <v>128458639</v>
       </c>
       <c r="B6" t="n">
-        <v>57713</v>
+        <v>57876</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,34 +1124,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>679701</v>
+        <v>679614</v>
       </c>
       <c r="R6" t="n">
-        <v>7118347</v>
+        <v>7118176</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,11 +1196,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre hack på låga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128458639</v>
+        <v>128458646</v>
       </c>
       <c r="B7" t="n">
-        <v>57876</v>
+        <v>57713</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,46 +1233,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>679614</v>
+        <v>679701</v>
       </c>
       <c r="R7" t="n">
-        <v>7118176</v>
+        <v>7118347</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,6 +1293,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre hack på låga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128458393</v>
+        <v>128458355</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1335,34 +1335,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>679637</v>
+        <v>679614</v>
       </c>
       <c r="R8" t="n">
-        <v>7118460</v>
+        <v>7118447</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,6 +1403,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128458355</v>
+        <v>128458393</v>
       </c>
       <c r="B9" t="n">
-        <v>57716</v>
+        <v>79116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1432,42 +1445,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>679614</v>
+        <v>679637</v>
       </c>
       <c r="R9" t="n">
-        <v>7118447</v>
+        <v>7118460</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,11 +1505,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128458380</v>
+        <v>128458361</v>
       </c>
       <c r="B11" t="n">
-        <v>91512</v>
+        <v>57716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>679630</v>
+        <v>679603</v>
       </c>
       <c r="R11" t="n">
-        <v>7118401</v>
+        <v>7118423</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,6 +1699,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128458684</v>
+        <v>128458345</v>
       </c>
       <c r="B12" t="n">
-        <v>79116</v>
+        <v>57876</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>679669</v>
+        <v>679629</v>
       </c>
       <c r="R12" t="n">
-        <v>7118266</v>
+        <v>7118222</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,45 +1827,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128458390</v>
+        <v>128458666</v>
       </c>
       <c r="B13" t="n">
-        <v>79116</v>
+        <v>98619</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679650</v>
+        <v>679677</v>
       </c>
       <c r="R13" t="n">
-        <v>7118244</v>
+        <v>7118227</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1895,12 +1912,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Blomställning</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1919,10 +1942,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128458345</v>
+        <v>128458380</v>
       </c>
       <c r="B14" t="n">
-        <v>57876</v>
+        <v>91512</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1930,21 +1953,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1977,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>679629</v>
+        <v>679630</v>
       </c>
       <c r="R14" t="n">
-        <v>7118222</v>
+        <v>7118401</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,57 +2039,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128458666</v>
+        <v>128458684</v>
       </c>
       <c r="B15" t="n">
-        <v>98619</v>
+        <v>79116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>679677</v>
+        <v>679669</v>
       </c>
       <c r="R15" t="n">
-        <v>7118227</v>
+        <v>7118266</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2101,18 +2112,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Blomställning</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2131,10 +2136,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128458361</v>
+        <v>128458390</v>
       </c>
       <c r="B16" t="n">
-        <v>57716</v>
+        <v>79116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,21 +2147,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2166,10 +2171,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>679603</v>
+        <v>679650</v>
       </c>
       <c r="R16" t="n">
-        <v>7118423</v>
+        <v>7118244</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,11 +2207,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2330,32 +2330,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128458392</v>
+        <v>128458339</v>
       </c>
       <c r="B18" t="n">
-        <v>79116</v>
+        <v>91459</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>679587</v>
+        <v>679682</v>
       </c>
       <c r="R18" t="n">
-        <v>7118403</v>
+        <v>7118294</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128458400</v>
+        <v>128458352</v>
       </c>
       <c r="B19" t="n">
-        <v>57716</v>
+        <v>57713</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2438,16 +2438,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>679599</v>
+        <v>679621</v>
       </c>
       <c r="R19" t="n">
-        <v>7118424</v>
+        <v>7118452</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2498,11 +2498,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2529,32 +2524,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128458339</v>
+        <v>128458400</v>
       </c>
       <c r="B20" t="n">
-        <v>91459</v>
+        <v>57716</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2564,10 +2559,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>679682</v>
+        <v>679599</v>
       </c>
       <c r="R20" t="n">
-        <v>7118294</v>
+        <v>7118424</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2600,6 +2595,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2626,10 +2626,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128458352</v>
+        <v>128458392</v>
       </c>
       <c r="B21" t="n">
-        <v>57713</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2637,21 +2637,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>679621</v>
+        <v>679587</v>
       </c>
       <c r="R21" t="n">
-        <v>7118452</v>
+        <v>7118403</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2820,7 +2820,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128458383</v>
+        <v>128458396</v>
       </c>
       <c r="B23" t="n">
         <v>79116</v>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>679564</v>
+        <v>679612</v>
       </c>
       <c r="R23" t="n">
-        <v>7118347</v>
+        <v>7118334</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,18 +2893,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2923,7 +2917,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128458396</v>
+        <v>128458383</v>
       </c>
       <c r="B24" t="n">
         <v>79116</v>
@@ -2958,10 +2952,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>679612</v>
+        <v>679564</v>
       </c>
       <c r="R24" t="n">
-        <v>7118334</v>
+        <v>7118347</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2996,12 +2990,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3316,32 +3316,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128458347</v>
+        <v>128458667</v>
       </c>
       <c r="B28" t="n">
-        <v>57876</v>
+        <v>75187</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6439</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>679582</v>
+        <v>679624</v>
       </c>
       <c r="R28" t="n">
-        <v>7118432</v>
+        <v>7118176</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3413,32 +3413,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128458667</v>
+        <v>128458347</v>
       </c>
       <c r="B29" t="n">
-        <v>75187</v>
+        <v>57876</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6439</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>679624</v>
+        <v>679582</v>
       </c>
       <c r="R29" t="n">
-        <v>7118176</v>
+        <v>7118432</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3510,32 +3510,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128458397</v>
+        <v>128458363</v>
       </c>
       <c r="B30" t="n">
-        <v>79116</v>
+        <v>80249</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>679666</v>
+        <v>679619</v>
       </c>
       <c r="R30" t="n">
-        <v>7118288</v>
+        <v>7118451</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3607,7 +3607,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128458683</v>
+        <v>128458397</v>
       </c>
       <c r="B31" t="n">
         <v>79116</v>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>679678</v>
+        <v>679666</v>
       </c>
       <c r="R31" t="n">
-        <v>7118309</v>
+        <v>7118288</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3704,32 +3704,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128458363</v>
+        <v>128458683</v>
       </c>
       <c r="B32" t="n">
-        <v>80249</v>
+        <v>79116</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>679619</v>
+        <v>679678</v>
       </c>
       <c r="R32" t="n">
-        <v>7118451</v>
+        <v>7118309</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3801,10 +3801,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128458649</v>
+        <v>128458395</v>
       </c>
       <c r="B33" t="n">
-        <v>57716</v>
+        <v>79116</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3812,21 +3812,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>679607</v>
+        <v>679643</v>
       </c>
       <c r="R33" t="n">
-        <v>7118183</v>
+        <v>7118369</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3872,11 +3872,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3903,10 +3898,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128458395</v>
+        <v>128458649</v>
       </c>
       <c r="B34" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,21 +3909,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,10 +3933,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>679643</v>
+        <v>679607</v>
       </c>
       <c r="R34" t="n">
-        <v>7118369</v>
+        <v>7118183</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3974,6 +3969,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4000,10 +4000,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458689</v>
+        <v>128458650</v>
       </c>
       <c r="B35" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4011,21 +4011,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4038,7 +4038,7 @@
         <v>679651</v>
       </c>
       <c r="R35" t="n">
-        <v>7118207</v>
+        <v>7118217</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4071,6 +4071,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4097,7 +4102,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458669</v>
+        <v>128458689</v>
       </c>
       <c r="B36" t="n">
         <v>79116</v>
@@ -4132,10 +4137,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679615</v>
+        <v>679651</v>
       </c>
       <c r="R36" t="n">
-        <v>7118231</v>
+        <v>7118207</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4170,18 +4175,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4297,10 +4296,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128458650</v>
+        <v>128458669</v>
       </c>
       <c r="B38" t="n">
-        <v>57716</v>
+        <v>79116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4308,21 +4307,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4332,10 +4331,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679651</v>
+        <v>679615</v>
       </c>
       <c r="R38" t="n">
-        <v>7118217</v>
+        <v>7118231</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4372,7 +4371,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4381,6 +4380,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4501,10 +4501,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128458685</v>
+        <v>128458354</v>
       </c>
       <c r="B40" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4512,21 +4512,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>679565</v>
+        <v>679621</v>
       </c>
       <c r="R40" t="n">
-        <v>7118208</v>
+        <v>7118296</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4572,6 +4572,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4598,32 +4603,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128458338</v>
+        <v>128458359</v>
       </c>
       <c r="B41" t="n">
-        <v>91459</v>
+        <v>57716</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4633,10 +4638,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>679591</v>
+        <v>679602</v>
       </c>
       <c r="R41" t="n">
-        <v>7118426</v>
+        <v>7118340</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4669,6 +4674,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4695,7 +4705,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128458398</v>
+        <v>128458685</v>
       </c>
       <c r="B42" t="n">
         <v>79116</v>
@@ -4730,10 +4740,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679689</v>
+        <v>679565</v>
       </c>
       <c r="R42" t="n">
-        <v>7118284</v>
+        <v>7118208</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4792,10 +4802,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128458354</v>
+        <v>128458398</v>
       </c>
       <c r="B43" t="n">
-        <v>57716</v>
+        <v>79116</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4803,21 +4813,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4827,10 +4837,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>679621</v>
+        <v>679689</v>
       </c>
       <c r="R43" t="n">
-        <v>7118296</v>
+        <v>7118284</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4863,11 +4873,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4894,32 +4899,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128458359</v>
+        <v>128458338</v>
       </c>
       <c r="B44" t="n">
-        <v>57716</v>
+        <v>91459</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4929,10 +4934,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>679602</v>
+        <v>679591</v>
       </c>
       <c r="R44" t="n">
-        <v>7118340</v>
+        <v>7118426</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4965,11 +4970,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5392,7 +5392,7 @@
         <v>128472156</v>
       </c>
       <c r="B49" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>128472170</v>
       </c>
       <c r="B50" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>128472174</v>
       </c>
       <c r="B51" t="n">
-        <v>98536</v>
+        <v>98542</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>128472149</v>
       </c>
       <c r="B52" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>128472158</v>
       </c>
       <c r="B53" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>128472169</v>
       </c>
       <c r="B54" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>128472148</v>
       </c>
       <c r="B57" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>128472172</v>
       </c>
       <c r="B58" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>128472159</v>
       </c>
       <c r="B59" t="n">
-        <v>80249</v>
+        <v>80253</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>128472157</v>
       </c>
       <c r="B60" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>128472168</v>
       </c>
       <c r="B62" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>128472167</v>
       </c>
       <c r="B63" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>128501348</v>
       </c>
       <c r="B64" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>128458651</v>
       </c>
       <c r="B5" t="n">
-        <v>97490</v>
+        <v>97503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128458639</v>
+        <v>128458646</v>
       </c>
       <c r="B6" t="n">
-        <v>57876</v>
+        <v>57713</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,46 +1124,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>679614</v>
+        <v>679701</v>
       </c>
       <c r="R6" t="n">
-        <v>7118176</v>
+        <v>7118347</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,6 +1184,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre hack på låga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128458646</v>
+        <v>128458639</v>
       </c>
       <c r="B7" t="n">
-        <v>57713</v>
+        <v>57876</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1233,34 +1226,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>679701</v>
+        <v>679614</v>
       </c>
       <c r="R7" t="n">
-        <v>7118347</v>
+        <v>7118176</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,11 +1298,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre hack på låga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128458355</v>
+        <v>128458393</v>
       </c>
       <c r="B8" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1335,42 +1335,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>679614</v>
+        <v>679637</v>
       </c>
       <c r="R8" t="n">
-        <v>7118447</v>
+        <v>7118460</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,11 +1395,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128458393</v>
+        <v>128458355</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,34 +1432,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>679637</v>
+        <v>679614</v>
       </c>
       <c r="R9" t="n">
-        <v>7118460</v>
+        <v>7118447</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,6 +1500,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128458361</v>
+        <v>128458390</v>
       </c>
       <c r="B11" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>679603</v>
+        <v>679650</v>
       </c>
       <c r="R11" t="n">
-        <v>7118423</v>
+        <v>7118244</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1699,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128458345</v>
+        <v>128458380</v>
       </c>
       <c r="B12" t="n">
-        <v>57876</v>
+        <v>91522</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>679629</v>
+        <v>679630</v>
       </c>
       <c r="R12" t="n">
-        <v>7118222</v>
+        <v>7118401</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,57 +1822,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128458666</v>
+        <v>128458361</v>
       </c>
       <c r="B13" t="n">
-        <v>98619</v>
+        <v>57716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679677</v>
+        <v>679603</v>
       </c>
       <c r="R13" t="n">
-        <v>7118227</v>
+        <v>7118423</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,7 +1897,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Blomställning</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1923,7 +1906,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1942,45 +1924,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128458380</v>
+        <v>128458666</v>
       </c>
       <c r="B14" t="n">
-        <v>91512</v>
+        <v>98632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>679630</v>
+        <v>679677</v>
       </c>
       <c r="R14" t="n">
-        <v>7118401</v>
+        <v>7118227</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,12 +2009,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Blomställning</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2042,7 +2042,7 @@
         <v>128458684</v>
       </c>
       <c r="B15" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,10 +2136,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128458390</v>
+        <v>128458345</v>
       </c>
       <c r="B16" t="n">
-        <v>79116</v>
+        <v>57876</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>679650</v>
+        <v>679629</v>
       </c>
       <c r="R16" t="n">
-        <v>7118244</v>
+        <v>7118222</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2330,32 +2330,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128458339</v>
+        <v>128458352</v>
       </c>
       <c r="B18" t="n">
-        <v>91459</v>
+        <v>57713</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>679682</v>
+        <v>679621</v>
       </c>
       <c r="R18" t="n">
-        <v>7118294</v>
+        <v>7118452</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128458352</v>
+        <v>128458400</v>
       </c>
       <c r="B19" t="n">
-        <v>57713</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2438,16 +2438,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>679621</v>
+        <v>679599</v>
       </c>
       <c r="R19" t="n">
-        <v>7118452</v>
+        <v>7118424</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2498,6 +2498,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2524,10 +2529,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128458400</v>
+        <v>128458392</v>
       </c>
       <c r="B20" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,21 +2540,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2559,10 +2564,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>679599</v>
+        <v>679587</v>
       </c>
       <c r="R20" t="n">
-        <v>7118424</v>
+        <v>7118403</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2595,11 +2600,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2626,32 +2626,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128458392</v>
+        <v>128458339</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>91469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>679587</v>
+        <v>679682</v>
       </c>
       <c r="R21" t="n">
-        <v>7118403</v>
+        <v>7118294</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2723,10 +2723,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128458690</v>
+        <v>128458383</v>
       </c>
       <c r="B22" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>679678</v>
+        <v>679564</v>
       </c>
       <c r="R22" t="n">
-        <v>7118225</v>
+        <v>7118347</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2796,12 +2796,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2823,7 +2829,7 @@
         <v>128458396</v>
       </c>
       <c r="B23" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,10 +2923,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128458383</v>
+        <v>128458690</v>
       </c>
       <c r="B24" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2952,10 +2958,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>679564</v>
+        <v>679678</v>
       </c>
       <c r="R24" t="n">
-        <v>7118347</v>
+        <v>7118225</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2990,18 +2996,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3020,10 +3020,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128458688</v>
+        <v>128458686</v>
       </c>
       <c r="B25" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>679619</v>
+        <v>679592</v>
       </c>
       <c r="R25" t="n">
-        <v>7118185</v>
+        <v>7118161</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3117,10 +3117,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128458686</v>
+        <v>128458688</v>
       </c>
       <c r="B26" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>679592</v>
+        <v>679619</v>
       </c>
       <c r="R26" t="n">
-        <v>7118161</v>
+        <v>7118185</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3316,32 +3316,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128458667</v>
+        <v>128458347</v>
       </c>
       <c r="B28" t="n">
-        <v>75187</v>
+        <v>57876</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6439</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>679624</v>
+        <v>679582</v>
       </c>
       <c r="R28" t="n">
-        <v>7118176</v>
+        <v>7118432</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3413,32 +3413,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128458347</v>
+        <v>128458667</v>
       </c>
       <c r="B29" t="n">
-        <v>57876</v>
+        <v>75188</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6439</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>679582</v>
+        <v>679624</v>
       </c>
       <c r="R29" t="n">
-        <v>7118432</v>
+        <v>7118176</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3510,32 +3510,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128458363</v>
+        <v>128458397</v>
       </c>
       <c r="B30" t="n">
-        <v>80249</v>
+        <v>79120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>679619</v>
+        <v>679666</v>
       </c>
       <c r="R30" t="n">
-        <v>7118451</v>
+        <v>7118288</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3607,10 +3607,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128458397</v>
+        <v>128458683</v>
       </c>
       <c r="B31" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>679666</v>
+        <v>679678</v>
       </c>
       <c r="R31" t="n">
-        <v>7118288</v>
+        <v>7118309</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3704,32 +3704,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128458683</v>
+        <v>128458363</v>
       </c>
       <c r="B32" t="n">
-        <v>79116</v>
+        <v>80253</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>679678</v>
+        <v>679619</v>
       </c>
       <c r="R32" t="n">
-        <v>7118309</v>
+        <v>7118451</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3804,7 +3804,7 @@
         <v>128458395</v>
       </c>
       <c r="B33" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4000,10 +4000,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458650</v>
+        <v>128458341</v>
       </c>
       <c r="B35" t="n">
-        <v>57716</v>
+        <v>79739</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4011,21 +4011,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>679651</v>
+        <v>679625</v>
       </c>
       <c r="R35" t="n">
-        <v>7118217</v>
+        <v>7118333</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4071,11 +4071,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4102,10 +4097,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458689</v>
+        <v>128458669</v>
       </c>
       <c r="B36" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4137,10 +4132,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679651</v>
+        <v>679615</v>
       </c>
       <c r="R36" t="n">
-        <v>7118207</v>
+        <v>7118231</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4175,12 +4170,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4199,10 +4200,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458341</v>
+        <v>128458689</v>
       </c>
       <c r="B37" t="n">
-        <v>79735</v>
+        <v>79120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4210,21 +4211,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4234,10 +4235,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679625</v>
+        <v>679651</v>
       </c>
       <c r="R37" t="n">
-        <v>7118333</v>
+        <v>7118207</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4296,10 +4297,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128458669</v>
+        <v>128458650</v>
       </c>
       <c r="B38" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4307,21 +4308,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4331,10 +4332,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679615</v>
+        <v>679651</v>
       </c>
       <c r="R38" t="n">
-        <v>7118231</v>
+        <v>7118217</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4371,7 +4372,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Med apotecier</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4380,7 +4381,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4501,10 +4501,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128458354</v>
+        <v>128458685</v>
       </c>
       <c r="B40" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4512,21 +4512,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>679621</v>
+        <v>679565</v>
       </c>
       <c r="R40" t="n">
-        <v>7118296</v>
+        <v>7118208</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4572,11 +4572,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4603,10 +4598,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128458359</v>
+        <v>128458398</v>
       </c>
       <c r="B41" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4614,21 +4609,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4638,10 +4633,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>679602</v>
+        <v>679689</v>
       </c>
       <c r="R41" t="n">
-        <v>7118340</v>
+        <v>7118284</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4674,11 +4669,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4705,32 +4695,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128458685</v>
+        <v>128458338</v>
       </c>
       <c r="B42" t="n">
-        <v>79116</v>
+        <v>91469</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4740,10 +4730,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679565</v>
+        <v>679591</v>
       </c>
       <c r="R42" t="n">
-        <v>7118208</v>
+        <v>7118426</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4802,32 +4792,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128458398</v>
+        <v>128458665</v>
       </c>
       <c r="B43" t="n">
-        <v>79116</v>
+        <v>58086</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4837,10 +4827,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>679689</v>
+        <v>679618</v>
       </c>
       <c r="R43" t="n">
-        <v>7118284</v>
+        <v>7118186</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4873,6 +4863,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>läte</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4899,32 +4894,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128458338</v>
+        <v>128458354</v>
       </c>
       <c r="B44" t="n">
-        <v>91459</v>
+        <v>57716</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4934,10 +4929,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>679591</v>
+        <v>679621</v>
       </c>
       <c r="R44" t="n">
-        <v>7118426</v>
+        <v>7118296</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4970,6 +4965,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4996,27 +4996,27 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128458665</v>
+        <v>128458359</v>
       </c>
       <c r="B45" t="n">
-        <v>58086</v>
+        <v>57716</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5031,10 +5031,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>679618</v>
+        <v>679602</v>
       </c>
       <c r="R45" t="n">
-        <v>7118186</v>
+        <v>7118340</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>läte</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5098,10 +5098,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128458682</v>
+        <v>128458394</v>
       </c>
       <c r="B46" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>679705</v>
+        <v>679604</v>
       </c>
       <c r="R46" t="n">
-        <v>7118324</v>
+        <v>7118405</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5195,10 +5195,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128458394</v>
+        <v>128458682</v>
       </c>
       <c r="B47" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>679604</v>
+        <v>679705</v>
       </c>
       <c r="R47" t="n">
-        <v>7118405</v>
+        <v>7118324</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5295,7 +5295,7 @@
         <v>128458391</v>
       </c>
       <c r="B48" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>128472156</v>
       </c>
       <c r="B49" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>128472174</v>
       </c>
       <c r="B51" t="n">
-        <v>98542</v>
+        <v>98549</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>128472149</v>
       </c>
       <c r="B52" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>128472158</v>
       </c>
       <c r="B53" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>128472148</v>
       </c>
       <c r="B57" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>128472157</v>
       </c>
       <c r="B60" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128458646</v>
+        <v>128458639</v>
       </c>
       <c r="B6" t="n">
-        <v>57713</v>
+        <v>57876</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,34 +1124,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>679701</v>
+        <v>679614</v>
       </c>
       <c r="R6" t="n">
-        <v>7118347</v>
+        <v>7118176</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,11 +1196,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre hack på låga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128458639</v>
+        <v>128458646</v>
       </c>
       <c r="B7" t="n">
-        <v>57876</v>
+        <v>57713</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,46 +1233,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>679614</v>
+        <v>679701</v>
       </c>
       <c r="R7" t="n">
-        <v>7118176</v>
+        <v>7118347</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,6 +1293,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre hack på låga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128458390</v>
+        <v>128458684</v>
       </c>
       <c r="B11" t="n">
         <v>79120</v>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>679650</v>
+        <v>679669</v>
       </c>
       <c r="R11" t="n">
-        <v>7118244</v>
+        <v>7118266</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128458380</v>
+        <v>128458361</v>
       </c>
       <c r="B12" t="n">
-        <v>91522</v>
+        <v>57716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>679630</v>
+        <v>679603</v>
       </c>
       <c r="R12" t="n">
-        <v>7118401</v>
+        <v>7118423</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,6 +1796,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128458361</v>
+        <v>128458345</v>
       </c>
       <c r="B13" t="n">
-        <v>57716</v>
+        <v>57876</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,21 +1838,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679603</v>
+        <v>679629</v>
       </c>
       <c r="R13" t="n">
-        <v>7118423</v>
+        <v>7118222</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1893,11 +1898,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,7 +2039,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128458684</v>
+        <v>128458390</v>
       </c>
       <c r="B15" t="n">
         <v>79120</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>679669</v>
+        <v>679650</v>
       </c>
       <c r="R15" t="n">
-        <v>7118266</v>
+        <v>7118244</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,10 +2136,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128458345</v>
+        <v>128458380</v>
       </c>
       <c r="B16" t="n">
-        <v>57876</v>
+        <v>91522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>679629</v>
+        <v>679630</v>
       </c>
       <c r="R16" t="n">
-        <v>7118222</v>
+        <v>7118401</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128458400</v>
+        <v>128458392</v>
       </c>
       <c r="B19" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>679599</v>
+        <v>679587</v>
       </c>
       <c r="R19" t="n">
-        <v>7118424</v>
+        <v>7118403</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2498,11 +2498,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2529,10 +2524,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128458392</v>
+        <v>128458400</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2540,21 +2535,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2564,10 +2559,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>679587</v>
+        <v>679599</v>
       </c>
       <c r="R20" t="n">
-        <v>7118403</v>
+        <v>7118424</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2600,6 +2595,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,7 +2723,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128458383</v>
+        <v>128458690</v>
       </c>
       <c r="B22" t="n">
         <v>79120</v>
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>679564</v>
+        <v>679678</v>
       </c>
       <c r="R22" t="n">
-        <v>7118347</v>
+        <v>7118225</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2796,18 +2796,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2923,7 +2917,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128458690</v>
+        <v>128458383</v>
       </c>
       <c r="B24" t="n">
         <v>79120</v>
@@ -2958,10 +2952,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>679678</v>
+        <v>679564</v>
       </c>
       <c r="R24" t="n">
-        <v>7118225</v>
+        <v>7118347</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2996,12 +2990,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128458686</v>
+        <v>128458688</v>
       </c>
       <c r="B25" t="n">
         <v>79120</v>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>679592</v>
+        <v>679619</v>
       </c>
       <c r="R25" t="n">
-        <v>7118161</v>
+        <v>7118185</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3117,7 +3117,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128458688</v>
+        <v>128458686</v>
       </c>
       <c r="B26" t="n">
         <v>79120</v>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>679619</v>
+        <v>679592</v>
       </c>
       <c r="R26" t="n">
-        <v>7118185</v>
+        <v>7118161</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3510,32 +3510,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128458397</v>
+        <v>128458363</v>
       </c>
       <c r="B30" t="n">
-        <v>79120</v>
+        <v>80253</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>679666</v>
+        <v>679619</v>
       </c>
       <c r="R30" t="n">
-        <v>7118288</v>
+        <v>7118451</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3607,7 +3607,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128458683</v>
+        <v>128458397</v>
       </c>
       <c r="B31" t="n">
         <v>79120</v>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>679678</v>
+        <v>679666</v>
       </c>
       <c r="R31" t="n">
-        <v>7118309</v>
+        <v>7118288</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3704,32 +3704,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128458363</v>
+        <v>128458683</v>
       </c>
       <c r="B32" t="n">
-        <v>80253</v>
+        <v>79120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>679619</v>
+        <v>679678</v>
       </c>
       <c r="R32" t="n">
-        <v>7118451</v>
+        <v>7118309</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4000,10 +4000,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458341</v>
+        <v>128458689</v>
       </c>
       <c r="B35" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4011,21 +4011,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>679625</v>
+        <v>679651</v>
       </c>
       <c r="R35" t="n">
-        <v>7118333</v>
+        <v>7118207</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4200,10 +4200,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458689</v>
+        <v>128458650</v>
       </c>
       <c r="B37" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4211,21 +4211,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4238,7 +4238,7 @@
         <v>679651</v>
       </c>
       <c r="R37" t="n">
-        <v>7118207</v>
+        <v>7118217</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4271,6 +4271,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4297,10 +4302,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128458650</v>
+        <v>128458341</v>
       </c>
       <c r="B38" t="n">
-        <v>57716</v>
+        <v>79739</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4308,21 +4313,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4332,10 +4337,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679651</v>
+        <v>679625</v>
       </c>
       <c r="R38" t="n">
-        <v>7118217</v>
+        <v>7118333</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4368,11 +4373,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4501,32 +4501,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128458685</v>
+        <v>128458665</v>
       </c>
       <c r="B40" t="n">
-        <v>79120</v>
+        <v>58086</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>679565</v>
+        <v>679618</v>
       </c>
       <c r="R40" t="n">
-        <v>7118208</v>
+        <v>7118186</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4572,6 +4572,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>läte</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4598,7 +4603,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128458398</v>
+        <v>128458685</v>
       </c>
       <c r="B41" t="n">
         <v>79120</v>
@@ -4633,10 +4638,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>679689</v>
+        <v>679565</v>
       </c>
       <c r="R41" t="n">
-        <v>7118284</v>
+        <v>7118208</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4695,32 +4700,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128458338</v>
+        <v>128458398</v>
       </c>
       <c r="B42" t="n">
-        <v>91469</v>
+        <v>79120</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4730,10 +4735,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679591</v>
+        <v>679689</v>
       </c>
       <c r="R42" t="n">
-        <v>7118426</v>
+        <v>7118284</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4792,27 +4797,27 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128458665</v>
+        <v>128458354</v>
       </c>
       <c r="B43" t="n">
-        <v>58086</v>
+        <v>57716</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4827,10 +4832,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>679618</v>
+        <v>679621</v>
       </c>
       <c r="R43" t="n">
-        <v>7118186</v>
+        <v>7118296</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4867,7 +4872,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>läte</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4894,7 +4899,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128458354</v>
+        <v>128458359</v>
       </c>
       <c r="B44" t="n">
         <v>57716</v>
@@ -4929,10 +4934,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>679621</v>
+        <v>679602</v>
       </c>
       <c r="R44" t="n">
-        <v>7118296</v>
+        <v>7118340</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4969,7 +4974,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4996,32 +5001,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128458359</v>
+        <v>128458338</v>
       </c>
       <c r="B45" t="n">
-        <v>57716</v>
+        <v>91469</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5031,10 +5036,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>679602</v>
+        <v>679591</v>
       </c>
       <c r="R45" t="n">
-        <v>7118340</v>
+        <v>7118426</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5067,11 +5072,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5098,7 +5098,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128458394</v>
+        <v>128458682</v>
       </c>
       <c r="B46" t="n">
         <v>79120</v>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>679604</v>
+        <v>679705</v>
       </c>
       <c r="R46" t="n">
-        <v>7118405</v>
+        <v>7118324</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5195,7 +5195,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128458682</v>
+        <v>128458394</v>
       </c>
       <c r="B47" t="n">
         <v>79120</v>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>679705</v>
+        <v>679604</v>
       </c>
       <c r="R47" t="n">
-        <v>7118324</v>
+        <v>7118405</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -1324,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128458393</v>
+        <v>128458355</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1335,34 +1335,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>679637</v>
+        <v>679614</v>
       </c>
       <c r="R8" t="n">
-        <v>7118460</v>
+        <v>7118447</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,6 +1403,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128458355</v>
+        <v>128458393</v>
       </c>
       <c r="B9" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1432,42 +1445,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>679614</v>
+        <v>679637</v>
       </c>
       <c r="R9" t="n">
-        <v>7118447</v>
+        <v>7118460</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,11 +1505,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2330,32 +2330,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128458352</v>
+        <v>128458339</v>
       </c>
       <c r="B18" t="n">
-        <v>57713</v>
+        <v>91469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>679621</v>
+        <v>679682</v>
       </c>
       <c r="R18" t="n">
-        <v>7118452</v>
+        <v>7118294</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128458392</v>
+        <v>128458352</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>679587</v>
+        <v>679621</v>
       </c>
       <c r="R19" t="n">
-        <v>7118403</v>
+        <v>7118452</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128458400</v>
+        <v>128458392</v>
       </c>
       <c r="B20" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>679599</v>
+        <v>679587</v>
       </c>
       <c r="R20" t="n">
-        <v>7118424</v>
+        <v>7118403</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2595,11 +2595,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2626,32 +2621,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128458339</v>
+        <v>128458400</v>
       </c>
       <c r="B21" t="n">
-        <v>91469</v>
+        <v>57716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2661,10 +2656,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>679682</v>
+        <v>679599</v>
       </c>
       <c r="R21" t="n">
-        <v>7118294</v>
+        <v>7118424</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2697,6 +2692,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4000,10 +4000,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458689</v>
+        <v>128458650</v>
       </c>
       <c r="B35" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4011,21 +4011,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4038,7 +4038,7 @@
         <v>679651</v>
       </c>
       <c r="R35" t="n">
-        <v>7118207</v>
+        <v>7118217</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4071,6 +4071,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4097,10 +4102,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458669</v>
+        <v>128458341</v>
       </c>
       <c r="B36" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4108,21 +4113,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4132,10 +4137,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679615</v>
+        <v>679625</v>
       </c>
       <c r="R36" t="n">
-        <v>7118231</v>
+        <v>7118333</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4170,18 +4175,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4200,10 +4199,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458650</v>
+        <v>128458689</v>
       </c>
       <c r="B37" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4211,21 +4210,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4238,7 +4237,7 @@
         <v>679651</v>
       </c>
       <c r="R37" t="n">
-        <v>7118217</v>
+        <v>7118207</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4271,11 +4270,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4302,10 +4296,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128458341</v>
+        <v>128458669</v>
       </c>
       <c r="B38" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4313,21 +4307,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4337,10 +4331,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679625</v>
+        <v>679615</v>
       </c>
       <c r="R38" t="n">
-        <v>7118333</v>
+        <v>7118231</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4375,12 +4369,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128458639</v>
+        <v>128458646</v>
       </c>
       <c r="B6" t="n">
-        <v>57876</v>
+        <v>57713</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,46 +1124,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>679614</v>
+        <v>679701</v>
       </c>
       <c r="R6" t="n">
-        <v>7118176</v>
+        <v>7118347</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,6 +1184,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre hack på låga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128458646</v>
+        <v>128458639</v>
       </c>
       <c r="B7" t="n">
-        <v>57713</v>
+        <v>57876</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1233,34 +1226,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>679701</v>
+        <v>679614</v>
       </c>
       <c r="R7" t="n">
-        <v>7118347</v>
+        <v>7118176</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,11 +1298,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre hack på låga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128458355</v>
+        <v>128458393</v>
       </c>
       <c r="B8" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1335,42 +1335,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>679614</v>
+        <v>679637</v>
       </c>
       <c r="R8" t="n">
-        <v>7118447</v>
+        <v>7118460</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,11 +1395,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128458393</v>
+        <v>128458355</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,34 +1432,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>679637</v>
+        <v>679614</v>
       </c>
       <c r="R9" t="n">
-        <v>7118460</v>
+        <v>7118447</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,6 +1500,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1725,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128458361</v>
+        <v>128458390</v>
       </c>
       <c r="B12" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>679603</v>
+        <v>679650</v>
       </c>
       <c r="R12" t="n">
-        <v>7118423</v>
+        <v>7118244</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,11 +1796,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128458345</v>
+        <v>128458380</v>
       </c>
       <c r="B13" t="n">
-        <v>57876</v>
+        <v>91522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679629</v>
+        <v>679630</v>
       </c>
       <c r="R13" t="n">
-        <v>7118222</v>
+        <v>7118401</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,57 +1919,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128458666</v>
+        <v>128458361</v>
       </c>
       <c r="B14" t="n">
-        <v>98632</v>
+        <v>57716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>679677</v>
+        <v>679603</v>
       </c>
       <c r="R14" t="n">
-        <v>7118227</v>
+        <v>7118423</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,7 +1994,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Blomställning</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2020,7 +2003,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2039,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128458390</v>
+        <v>128458345</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>57876</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2050,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2074,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>679650</v>
+        <v>679629</v>
       </c>
       <c r="R15" t="n">
-        <v>7118244</v>
+        <v>7118222</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,45 +2118,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128458380</v>
+        <v>128458666</v>
       </c>
       <c r="B16" t="n">
-        <v>91522</v>
+        <v>98632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>679630</v>
+        <v>679677</v>
       </c>
       <c r="R16" t="n">
-        <v>7118401</v>
+        <v>7118227</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,12 +2203,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Blomställning</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128458352</v>
+        <v>128458392</v>
       </c>
       <c r="B19" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>679621</v>
+        <v>679587</v>
       </c>
       <c r="R19" t="n">
-        <v>7118452</v>
+        <v>7118403</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128458392</v>
+        <v>128458352</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>679587</v>
+        <v>679621</v>
       </c>
       <c r="R20" t="n">
-        <v>7118403</v>
+        <v>7118452</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3020,10 +3020,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128458688</v>
+        <v>128458360</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3031,21 +3031,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>679619</v>
+        <v>679584</v>
       </c>
       <c r="R25" t="n">
-        <v>7118185</v>
+        <v>7118426</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3091,6 +3091,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3117,7 +3122,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128458686</v>
+        <v>128458688</v>
       </c>
       <c r="B26" t="n">
         <v>79120</v>
@@ -3152,10 +3157,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>679592</v>
+        <v>679619</v>
       </c>
       <c r="R26" t="n">
-        <v>7118161</v>
+        <v>7118185</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3214,10 +3219,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128458360</v>
+        <v>128458686</v>
       </c>
       <c r="B27" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3225,21 +3230,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3249,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>679584</v>
+        <v>679592</v>
       </c>
       <c r="R27" t="n">
-        <v>7118426</v>
+        <v>7118161</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3285,11 +3290,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3316,32 +3316,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128458347</v>
+        <v>128458667</v>
       </c>
       <c r="B28" t="n">
-        <v>57876</v>
+        <v>75188</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6439</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>679582</v>
+        <v>679624</v>
       </c>
       <c r="R28" t="n">
-        <v>7118432</v>
+        <v>7118176</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3413,32 +3413,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128458667</v>
+        <v>128458347</v>
       </c>
       <c r="B29" t="n">
-        <v>75188</v>
+        <v>57876</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6439</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>679624</v>
+        <v>679582</v>
       </c>
       <c r="R29" t="n">
-        <v>7118176</v>
+        <v>7118432</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3510,32 +3510,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128458363</v>
+        <v>128458397</v>
       </c>
       <c r="B30" t="n">
-        <v>80253</v>
+        <v>79120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>679619</v>
+        <v>679666</v>
       </c>
       <c r="R30" t="n">
-        <v>7118451</v>
+        <v>7118288</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3607,32 +3607,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128458397</v>
+        <v>128458363</v>
       </c>
       <c r="B31" t="n">
-        <v>79120</v>
+        <v>80253</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>679666</v>
+        <v>679619</v>
       </c>
       <c r="R31" t="n">
-        <v>7118288</v>
+        <v>7118451</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4000,10 +4000,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458650</v>
+        <v>128458341</v>
       </c>
       <c r="B35" t="n">
-        <v>57716</v>
+        <v>79739</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4011,21 +4011,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>679651</v>
+        <v>679625</v>
       </c>
       <c r="R35" t="n">
-        <v>7118217</v>
+        <v>7118333</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4071,11 +4071,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4102,10 +4097,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458341</v>
+        <v>128458669</v>
       </c>
       <c r="B36" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4113,21 +4108,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4137,10 +4132,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679625</v>
+        <v>679615</v>
       </c>
       <c r="R36" t="n">
-        <v>7118333</v>
+        <v>7118231</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4175,12 +4170,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4296,10 +4297,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128458669</v>
+        <v>128458650</v>
       </c>
       <c r="B38" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4307,21 +4308,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4331,10 +4332,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679615</v>
+        <v>679651</v>
       </c>
       <c r="R38" t="n">
-        <v>7118231</v>
+        <v>7118217</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4371,7 +4372,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Med apotecier</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4380,7 +4381,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4603,10 +4603,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128458685</v>
+        <v>128458354</v>
       </c>
       <c r="B41" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4614,21 +4614,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4638,10 +4638,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>679565</v>
+        <v>679621</v>
       </c>
       <c r="R41" t="n">
-        <v>7118208</v>
+        <v>7118296</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4674,6 +4674,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4700,10 +4705,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128458398</v>
+        <v>128458359</v>
       </c>
       <c r="B42" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4711,21 +4716,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4735,10 +4740,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679689</v>
+        <v>679602</v>
       </c>
       <c r="R42" t="n">
-        <v>7118284</v>
+        <v>7118340</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4771,6 +4776,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4797,10 +4807,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128458354</v>
+        <v>128458685</v>
       </c>
       <c r="B43" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4808,21 +4818,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4832,10 +4842,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>679621</v>
+        <v>679565</v>
       </c>
       <c r="R43" t="n">
-        <v>7118296</v>
+        <v>7118208</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4868,11 +4878,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4899,32 +4904,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128458359</v>
+        <v>128458338</v>
       </c>
       <c r="B44" t="n">
-        <v>57716</v>
+        <v>91469</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4934,10 +4939,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>679602</v>
+        <v>679591</v>
       </c>
       <c r="R44" t="n">
-        <v>7118340</v>
+        <v>7118426</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4970,11 +4975,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5001,32 +5001,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128458338</v>
+        <v>128458398</v>
       </c>
       <c r="B45" t="n">
-        <v>91469</v>
+        <v>79120</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>679591</v>
+        <v>679689</v>
       </c>
       <c r="R45" t="n">
-        <v>7118426</v>
+        <v>7118284</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5392,7 +5392,7 @@
         <v>128472156</v>
       </c>
       <c r="B49" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>128472170</v>
       </c>
       <c r="B50" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>128472174</v>
       </c>
       <c r="B51" t="n">
-        <v>98549</v>
+        <v>98553</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>128472149</v>
       </c>
       <c r="B52" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>128472158</v>
       </c>
       <c r="B53" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>128472169</v>
       </c>
       <c r="B54" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>128472165</v>
       </c>
       <c r="B55" t="n">
-        <v>57820</v>
+        <v>57824</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>128472166</v>
       </c>
       <c r="B56" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>128472148</v>
       </c>
       <c r="B57" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>128472172</v>
       </c>
       <c r="B58" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>128472159</v>
       </c>
       <c r="B59" t="n">
-        <v>80253</v>
+        <v>80257</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>128472157</v>
       </c>
       <c r="B60" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>128472171</v>
       </c>
       <c r="B61" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>128472168</v>
       </c>
       <c r="B62" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>128472167</v>
       </c>
       <c r="B63" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>128501348</v>
       </c>
       <c r="B64" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>128458343</v>
       </c>
       <c r="B4" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>128458651</v>
       </c>
       <c r="B5" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128458646</v>
+        <v>128458639</v>
       </c>
       <c r="B6" t="n">
-        <v>57713</v>
+        <v>57880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,34 +1124,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>679701</v>
+        <v>679614</v>
       </c>
       <c r="R6" t="n">
-        <v>7118347</v>
+        <v>7118176</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,11 +1196,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre hack på låga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128458639</v>
+        <v>128458646</v>
       </c>
       <c r="B7" t="n">
-        <v>57876</v>
+        <v>57717</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,46 +1233,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>679614</v>
+        <v>679701</v>
       </c>
       <c r="R7" t="n">
-        <v>7118176</v>
+        <v>7118347</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,6 +1293,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre hack på låga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,7 +1327,7 @@
         <v>128458393</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>128458355</v>
       </c>
       <c r="B9" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>128458379</v>
       </c>
       <c r="B10" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>128458684</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>128458390</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>128458380</v>
       </c>
       <c r="B13" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>128458361</v>
       </c>
       <c r="B14" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>128458345</v>
       </c>
       <c r="B15" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>128458666</v>
       </c>
       <c r="B16" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>128458348</v>
       </c>
       <c r="B17" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,32 +2330,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128458339</v>
+        <v>128458392</v>
       </c>
       <c r="B18" t="n">
-        <v>91469</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>679682</v>
+        <v>679587</v>
       </c>
       <c r="R18" t="n">
-        <v>7118294</v>
+        <v>7118403</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,32 +2427,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128458392</v>
+        <v>128458339</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>91473</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>679587</v>
+        <v>679682</v>
       </c>
       <c r="R19" t="n">
-        <v>7118403</v>
+        <v>7118294</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2527,7 +2527,7 @@
         <v>128458352</v>
       </c>
       <c r="B20" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>128458400</v>
       </c>
       <c r="B21" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>128458690</v>
       </c>
       <c r="B22" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>128458396</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>128458383</v>
       </c>
       <c r="B24" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3020,10 +3020,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128458360</v>
+        <v>128458688</v>
       </c>
       <c r="B25" t="n">
-        <v>57716</v>
+        <v>79124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3031,21 +3031,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>679584</v>
+        <v>679619</v>
       </c>
       <c r="R25" t="n">
-        <v>7118426</v>
+        <v>7118185</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3091,11 +3091,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3122,10 +3117,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128458688</v>
+        <v>128458686</v>
       </c>
       <c r="B26" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3157,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>679619</v>
+        <v>679592</v>
       </c>
       <c r="R26" t="n">
-        <v>7118185</v>
+        <v>7118161</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3219,10 +3214,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128458686</v>
+        <v>128458360</v>
       </c>
       <c r="B27" t="n">
-        <v>79120</v>
+        <v>57720</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3230,21 +3225,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3254,10 +3249,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>679592</v>
+        <v>679584</v>
       </c>
       <c r="R27" t="n">
-        <v>7118161</v>
+        <v>7118426</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3290,6 +3285,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3319,7 +3319,7 @@
         <v>128458667</v>
       </c>
       <c r="B28" t="n">
-        <v>75188</v>
+        <v>75192</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>128458347</v>
       </c>
       <c r="B29" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>128458397</v>
       </c>
       <c r="B30" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3607,32 +3607,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128458363</v>
+        <v>128458683</v>
       </c>
       <c r="B31" t="n">
-        <v>80253</v>
+        <v>79124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>679619</v>
+        <v>679678</v>
       </c>
       <c r="R31" t="n">
-        <v>7118451</v>
+        <v>7118309</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3704,32 +3704,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128458683</v>
+        <v>128458363</v>
       </c>
       <c r="B32" t="n">
-        <v>79120</v>
+        <v>80257</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>679678</v>
+        <v>679619</v>
       </c>
       <c r="R32" t="n">
-        <v>7118309</v>
+        <v>7118451</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3804,7 +3804,7 @@
         <v>128458395</v>
       </c>
       <c r="B33" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>128458649</v>
       </c>
       <c r="B34" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4000,10 +4000,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458341</v>
+        <v>128458689</v>
       </c>
       <c r="B35" t="n">
-        <v>79739</v>
+        <v>79124</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4011,21 +4011,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>679625</v>
+        <v>679651</v>
       </c>
       <c r="R35" t="n">
-        <v>7118333</v>
+        <v>7118207</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4097,10 +4097,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458669</v>
+        <v>128458341</v>
       </c>
       <c r="B36" t="n">
-        <v>79120</v>
+        <v>79743</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4108,21 +4108,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679615</v>
+        <v>679625</v>
       </c>
       <c r="R36" t="n">
-        <v>7118231</v>
+        <v>7118333</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4170,18 +4170,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4200,10 +4194,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458689</v>
+        <v>128458669</v>
       </c>
       <c r="B37" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4235,10 +4229,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679651</v>
+        <v>679615</v>
       </c>
       <c r="R37" t="n">
-        <v>7118207</v>
+        <v>7118231</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4273,12 +4267,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4300,7 +4300,7 @@
         <v>128458650</v>
       </c>
       <c r="B38" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>128458357</v>
       </c>
       <c r="B39" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4501,10 +4501,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128458665</v>
+        <v>128458338</v>
       </c>
       <c r="B40" t="n">
-        <v>58086</v>
+        <v>91473</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4512,21 +4512,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>679618</v>
+        <v>679591</v>
       </c>
       <c r="R40" t="n">
-        <v>7118186</v>
+        <v>7118426</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4572,11 +4572,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>läte</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4603,10 +4598,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128458354</v>
+        <v>128458685</v>
       </c>
       <c r="B41" t="n">
-        <v>57716</v>
+        <v>79124</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4614,21 +4609,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4638,10 +4633,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>679621</v>
+        <v>679565</v>
       </c>
       <c r="R41" t="n">
-        <v>7118296</v>
+        <v>7118208</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4674,11 +4669,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4705,10 +4695,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128458359</v>
+        <v>128458398</v>
       </c>
       <c r="B42" t="n">
-        <v>57716</v>
+        <v>79124</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4716,21 +4706,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4740,10 +4730,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679602</v>
+        <v>679689</v>
       </c>
       <c r="R42" t="n">
-        <v>7118340</v>
+        <v>7118284</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4776,11 +4766,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4807,10 +4792,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128458685</v>
+        <v>128458354</v>
       </c>
       <c r="B43" t="n">
-        <v>79120</v>
+        <v>57720</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4818,21 +4803,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4842,10 +4827,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>679565</v>
+        <v>679621</v>
       </c>
       <c r="R43" t="n">
-        <v>7118208</v>
+        <v>7118296</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4878,6 +4863,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4904,32 +4894,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128458338</v>
+        <v>128458359</v>
       </c>
       <c r="B44" t="n">
-        <v>91469</v>
+        <v>57720</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4939,10 +4929,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>679591</v>
+        <v>679602</v>
       </c>
       <c r="R44" t="n">
-        <v>7118426</v>
+        <v>7118340</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4975,6 +4965,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5001,32 +4996,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128458398</v>
+        <v>128458665</v>
       </c>
       <c r="B45" t="n">
-        <v>79120</v>
+        <v>58090</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5036,10 +5031,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>679689</v>
+        <v>679618</v>
       </c>
       <c r="R45" t="n">
-        <v>7118284</v>
+        <v>7118186</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5072,6 +5067,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>läte</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5101,7 +5101,7 @@
         <v>128458682</v>
       </c>
       <c r="B46" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>128458394</v>
       </c>
       <c r="B47" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>128458391</v>
       </c>
       <c r="B48" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -1324,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128458393</v>
+        <v>128458355</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1335,34 +1335,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>679637</v>
+        <v>679614</v>
       </c>
       <c r="R8" t="n">
-        <v>7118460</v>
+        <v>7118447</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,6 +1403,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128458355</v>
+        <v>128458393</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1432,42 +1445,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>679614</v>
+        <v>679637</v>
       </c>
       <c r="R9" t="n">
-        <v>7118447</v>
+        <v>7118460</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,11 +1505,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -3801,10 +3801,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128458395</v>
+        <v>128458649</v>
       </c>
       <c r="B33" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3812,21 +3812,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>679643</v>
+        <v>679607</v>
       </c>
       <c r="R33" t="n">
-        <v>7118369</v>
+        <v>7118183</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3872,6 +3872,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3898,10 +3903,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128458649</v>
+        <v>128458395</v>
       </c>
       <c r="B34" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3909,21 +3914,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3933,10 +3938,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>679607</v>
+        <v>679643</v>
       </c>
       <c r="R34" t="n">
-        <v>7118183</v>
+        <v>7118369</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3969,11 +3974,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4000,10 +4000,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458689</v>
+        <v>128458650</v>
       </c>
       <c r="B35" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4011,21 +4011,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4038,7 +4038,7 @@
         <v>679651</v>
       </c>
       <c r="R35" t="n">
-        <v>7118207</v>
+        <v>7118217</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4071,6 +4071,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4097,10 +4102,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458341</v>
+        <v>128458689</v>
       </c>
       <c r="B36" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4108,21 +4113,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4132,10 +4137,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679625</v>
+        <v>679651</v>
       </c>
       <c r="R36" t="n">
-        <v>7118333</v>
+        <v>7118207</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,10 +4199,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458669</v>
+        <v>128458341</v>
       </c>
       <c r="B37" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4205,21 +4210,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4229,10 +4234,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679615</v>
+        <v>679625</v>
       </c>
       <c r="R37" t="n">
-        <v>7118231</v>
+        <v>7118333</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4267,18 +4272,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4297,10 +4296,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128458650</v>
+        <v>128458669</v>
       </c>
       <c r="B38" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4308,21 +4307,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4332,10 +4331,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679651</v>
+        <v>679615</v>
       </c>
       <c r="R38" t="n">
-        <v>7118217</v>
+        <v>7118231</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4372,7 +4371,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4381,6 +4380,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4501,32 +4501,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128458338</v>
+        <v>128458354</v>
       </c>
       <c r="B40" t="n">
-        <v>91473</v>
+        <v>57720</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>679591</v>
+        <v>679621</v>
       </c>
       <c r="R40" t="n">
-        <v>7118426</v>
+        <v>7118296</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4572,6 +4572,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4598,10 +4603,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128458685</v>
+        <v>128458359</v>
       </c>
       <c r="B41" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4609,21 +4614,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4633,10 +4638,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>679565</v>
+        <v>679602</v>
       </c>
       <c r="R41" t="n">
-        <v>7118208</v>
+        <v>7118340</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4669,6 +4674,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4695,7 +4705,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128458398</v>
+        <v>128458685</v>
       </c>
       <c r="B42" t="n">
         <v>79124</v>
@@ -4730,10 +4740,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679689</v>
+        <v>679565</v>
       </c>
       <c r="R42" t="n">
-        <v>7118284</v>
+        <v>7118208</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4792,10 +4802,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128458354</v>
+        <v>128458398</v>
       </c>
       <c r="B43" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4803,21 +4813,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4827,10 +4837,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>679621</v>
+        <v>679689</v>
       </c>
       <c r="R43" t="n">
-        <v>7118296</v>
+        <v>7118284</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4863,11 +4873,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4894,32 +4899,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128458359</v>
+        <v>128458338</v>
       </c>
       <c r="B44" t="n">
-        <v>57720</v>
+        <v>91473</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4929,10 +4934,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>679602</v>
+        <v>679591</v>
       </c>
       <c r="R44" t="n">
-        <v>7118340</v>
+        <v>7118426</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4965,11 +4970,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>128458343</v>
       </c>
       <c r="B4" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>128458651</v>
       </c>
       <c r="B5" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128458639</v>
+        <v>128458646</v>
       </c>
       <c r="B6" t="n">
-        <v>57880</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,46 +1124,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>679614</v>
+        <v>679701</v>
       </c>
       <c r="R6" t="n">
-        <v>7118176</v>
+        <v>7118347</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,6 +1184,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre hack på låga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128458646</v>
+        <v>128458639</v>
       </c>
       <c r="B7" t="n">
-        <v>57717</v>
+        <v>57883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1233,34 +1226,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>679701</v>
+        <v>679614</v>
       </c>
       <c r="R7" t="n">
-        <v>7118347</v>
+        <v>7118176</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,11 +1298,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre hack på låga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,7 +1327,7 @@
         <v>128458355</v>
       </c>
       <c r="B8" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128458393</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>128458379</v>
       </c>
       <c r="B10" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128458684</v>
+        <v>128458380</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>91531</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>679669</v>
+        <v>679630</v>
       </c>
       <c r="R11" t="n">
-        <v>7118266</v>
+        <v>7118401</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128458390</v>
+        <v>128458361</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>679650</v>
+        <v>679603</v>
       </c>
       <c r="R12" t="n">
-        <v>7118244</v>
+        <v>7118423</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,6 +1796,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128458380</v>
+        <v>128458684</v>
       </c>
       <c r="B13" t="n">
-        <v>91526</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,21 +1838,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679630</v>
+        <v>679669</v>
       </c>
       <c r="R13" t="n">
-        <v>7118401</v>
+        <v>7118266</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128458361</v>
+        <v>128458390</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1930,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>679603</v>
+        <v>679650</v>
       </c>
       <c r="R14" t="n">
-        <v>7118423</v>
+        <v>7118244</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1990,11 +1995,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2024,7 +2024,7 @@
         <v>128458345</v>
       </c>
       <c r="B15" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>128458666</v>
       </c>
       <c r="B16" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>128458348</v>
       </c>
       <c r="B17" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,32 +2330,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128458392</v>
+        <v>128458339</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>91478</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>679587</v>
+        <v>679682</v>
       </c>
       <c r="R18" t="n">
-        <v>7118403</v>
+        <v>7118294</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,32 +2427,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128458339</v>
+        <v>128458352</v>
       </c>
       <c r="B19" t="n">
-        <v>91473</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>679682</v>
+        <v>679621</v>
       </c>
       <c r="R19" t="n">
-        <v>7118294</v>
+        <v>7118452</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128458352</v>
+        <v>128458400</v>
       </c>
       <c r="B20" t="n">
-        <v>57717</v>
+        <v>57723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,16 +2535,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>679621</v>
+        <v>679599</v>
       </c>
       <c r="R20" t="n">
-        <v>7118452</v>
+        <v>7118424</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2595,6 +2595,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2621,10 +2626,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128458400</v>
+        <v>128458392</v>
       </c>
       <c r="B21" t="n">
-        <v>57720</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2632,21 +2637,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2656,10 +2661,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>679599</v>
+        <v>679587</v>
       </c>
       <c r="R21" t="n">
-        <v>7118424</v>
+        <v>7118403</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2692,11 +2697,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Bohål på granlåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2726,7 +2726,7 @@
         <v>128458690</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>128458396</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>128458383</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>128458688</v>
       </c>
       <c r="B25" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>128458686</v>
       </c>
       <c r="B26" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>128458360</v>
       </c>
       <c r="B27" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>128458667</v>
       </c>
       <c r="B28" t="n">
-        <v>75192</v>
+        <v>82988</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>128458347</v>
       </c>
       <c r="B29" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3510,32 +3510,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128458397</v>
+        <v>128458363</v>
       </c>
       <c r="B30" t="n">
-        <v>79124</v>
+        <v>80162</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>679666</v>
+        <v>679619</v>
       </c>
       <c r="R30" t="n">
-        <v>7118288</v>
+        <v>7118451</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3607,10 +3607,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128458683</v>
+        <v>128458397</v>
       </c>
       <c r="B31" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>679678</v>
+        <v>679666</v>
       </c>
       <c r="R31" t="n">
-        <v>7118309</v>
+        <v>7118288</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3704,32 +3704,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128458363</v>
+        <v>128458683</v>
       </c>
       <c r="B32" t="n">
-        <v>80257</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>679619</v>
+        <v>679678</v>
       </c>
       <c r="R32" t="n">
-        <v>7118451</v>
+        <v>7118309</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3801,10 +3801,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128458649</v>
+        <v>128458395</v>
       </c>
       <c r="B33" t="n">
-        <v>57720</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3812,21 +3812,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>679607</v>
+        <v>679643</v>
       </c>
       <c r="R33" t="n">
-        <v>7118183</v>
+        <v>7118369</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3872,11 +3872,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3903,10 +3898,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128458395</v>
+        <v>128458649</v>
       </c>
       <c r="B34" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,21 +3909,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,10 +3933,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>679643</v>
+        <v>679607</v>
       </c>
       <c r="R34" t="n">
-        <v>7118369</v>
+        <v>7118183</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3974,6 +3969,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4003,7 +4003,7 @@
         <v>128458650</v>
       </c>
       <c r="B35" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>128458689</v>
       </c>
       <c r="B36" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>128458341</v>
       </c>
       <c r="B37" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>128458669</v>
       </c>
       <c r="B38" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>128458357</v>
       </c>
       <c r="B39" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4501,32 +4501,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128458354</v>
+        <v>128458338</v>
       </c>
       <c r="B40" t="n">
-        <v>57720</v>
+        <v>91478</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>679621</v>
+        <v>679591</v>
       </c>
       <c r="R40" t="n">
-        <v>7118296</v>
+        <v>7118426</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4572,11 +4572,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4603,27 +4598,27 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128458359</v>
+        <v>128458665</v>
       </c>
       <c r="B41" t="n">
-        <v>57720</v>
+        <v>58093</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4638,10 +4633,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>679602</v>
+        <v>679618</v>
       </c>
       <c r="R41" t="n">
-        <v>7118340</v>
+        <v>7118186</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4678,7 +4673,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>läte</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4705,10 +4700,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128458685</v>
+        <v>128458354</v>
       </c>
       <c r="B42" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4716,21 +4711,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4740,10 +4735,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679565</v>
+        <v>679621</v>
       </c>
       <c r="R42" t="n">
-        <v>7118208</v>
+        <v>7118296</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4776,6 +4771,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4802,10 +4802,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128458398</v>
+        <v>128458359</v>
       </c>
       <c r="B43" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4813,21 +4813,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>679689</v>
+        <v>679602</v>
       </c>
       <c r="R43" t="n">
-        <v>7118284</v>
+        <v>7118340</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4873,6 +4873,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4899,32 +4904,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128458338</v>
+        <v>128458685</v>
       </c>
       <c r="B44" t="n">
-        <v>91473</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4934,10 +4939,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>679591</v>
+        <v>679565</v>
       </c>
       <c r="R44" t="n">
-        <v>7118426</v>
+        <v>7118208</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4996,32 +5001,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128458665</v>
+        <v>128458398</v>
       </c>
       <c r="B45" t="n">
-        <v>58090</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5031,10 +5036,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>679618</v>
+        <v>679689</v>
       </c>
       <c r="R45" t="n">
-        <v>7118186</v>
+        <v>7118284</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5067,11 +5072,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>läte</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5101,7 +5101,7 @@
         <v>128458682</v>
       </c>
       <c r="B46" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>128458394</v>
       </c>
       <c r="B47" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>128458391</v>
       </c>
       <c r="B48" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>128472156</v>
       </c>
       <c r="B49" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>128472170</v>
       </c>
       <c r="B50" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>128472174</v>
       </c>
       <c r="B51" t="n">
-        <v>98553</v>
+        <v>98560</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>128472149</v>
       </c>
       <c r="B52" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>128472158</v>
       </c>
       <c r="B53" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>128472169</v>
       </c>
       <c r="B54" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>128472165</v>
       </c>
       <c r="B55" t="n">
-        <v>57824</v>
+        <v>57827</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>128472166</v>
       </c>
       <c r="B56" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>128472148</v>
       </c>
       <c r="B57" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>128472172</v>
       </c>
       <c r="B58" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>128472159</v>
       </c>
       <c r="B59" t="n">
-        <v>80257</v>
+        <v>80162</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>128472157</v>
       </c>
       <c r="B60" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>128472171</v>
       </c>
       <c r="B61" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>128472168</v>
       </c>
       <c r="B62" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>128472167</v>
       </c>
       <c r="B63" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>128501348</v>
       </c>
       <c r="B64" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -6847,7 +6847,7 @@
         <v>128501348</v>
       </c>
       <c r="B64" t="n">
-        <v>83005</v>
+        <v>83010</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6943,6 +6943,536 @@
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129224130</v>
+      </c>
+      <c r="B65" t="n">
+        <v>91522</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Vargträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>679702</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7118430</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129224131</v>
+      </c>
+      <c r="B66" t="n">
+        <v>91544</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Vargträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>679728</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7118383</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129224133</v>
+      </c>
+      <c r="B67" t="n">
+        <v>92226</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Vargträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>679718</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7118300</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129224129</v>
+      </c>
+      <c r="B68" t="n">
+        <v>91544</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Vargträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>679626</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7118415</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129224134</v>
+      </c>
+      <c r="B69" t="n">
+        <v>91544</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Vargträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>679694</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7118257</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -6948,7 +6948,7 @@
         <v>129224130</v>
       </c>
       <c r="B65" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>129224131</v>
       </c>
       <c r="B66" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>129224133</v>
       </c>
       <c r="B67" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>129224129</v>
       </c>
       <c r="B68" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>129224134</v>
       </c>
       <c r="B69" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -6948,7 +6948,7 @@
         <v>129224130</v>
       </c>
       <c r="B65" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>129224131</v>
       </c>
       <c r="B66" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>129224133</v>
       </c>
       <c r="B67" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>129224129</v>
       </c>
       <c r="B68" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>129224134</v>
       </c>
       <c r="B69" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -6948,7 +6948,7 @@
         <v>129224130</v>
       </c>
       <c r="B65" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>129224131</v>
       </c>
       <c r="B66" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>129224133</v>
       </c>
       <c r="B67" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>129224129</v>
       </c>
       <c r="B68" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>129224134</v>
       </c>
       <c r="B69" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -6948,7 +6948,7 @@
         <v>129224130</v>
       </c>
       <c r="B65" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>129224131</v>
       </c>
       <c r="B66" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>129224133</v>
       </c>
       <c r="B67" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>129224129</v>
       </c>
       <c r="B68" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>129224134</v>
       </c>
       <c r="B69" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -7054,7 +7054,7 @@
         <v>129224131</v>
       </c>
       <c r="B66" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7071,14 +7071,10 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>1</t>
@@ -7160,7 +7156,7 @@
         <v>129224133</v>
       </c>
       <c r="B67" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7266,7 +7262,7 @@
         <v>129224129</v>
       </c>
       <c r="B68" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7283,14 +7279,10 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>1</t>
@@ -7372,7 +7364,7 @@
         <v>129224134</v>
       </c>
       <c r="B69" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7389,14 +7381,10 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>1</t>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -6948,7 +6948,7 @@
         <v>129224130</v>
       </c>
       <c r="B65" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>129224131</v>
       </c>
       <c r="B66" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>129224133</v>
       </c>
       <c r="B67" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>129224129</v>
       </c>
       <c r="B68" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>129224134</v>
       </c>
       <c r="B69" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -6948,7 +6948,7 @@
         <v>129224130</v>
       </c>
       <c r="B65" t="n">
-        <v>91539</v>
+        <v>91541</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>129224131</v>
       </c>
       <c r="B66" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>129224133</v>
       </c>
       <c r="B67" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>129224129</v>
       </c>
       <c r="B68" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>129224134</v>
       </c>
       <c r="B69" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -6948,7 +6948,7 @@
         <v>129224130</v>
       </c>
       <c r="B65" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>129224131</v>
       </c>
       <c r="B66" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>129224133</v>
       </c>
       <c r="B67" t="n">
-        <v>92263</v>
+        <v>92267</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>129224129</v>
       </c>
       <c r="B68" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>129224134</v>
       </c>
       <c r="B69" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -6948,7 +6948,7 @@
         <v>129224130</v>
       </c>
       <c r="B65" t="n">
-        <v>91545</v>
+        <v>91546</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>129224131</v>
       </c>
       <c r="B66" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>129224133</v>
       </c>
       <c r="B67" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>129224129</v>
       </c>
       <c r="B68" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>129224134</v>
       </c>
       <c r="B69" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -6948,7 +6948,7 @@
         <v>129224130</v>
       </c>
       <c r="B65" t="n">
-        <v>91546</v>
+        <v>91549</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>129224131</v>
       </c>
       <c r="B66" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>129224133</v>
       </c>
       <c r="B67" t="n">
-        <v>92268</v>
+        <v>92271</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>129224129</v>
       </c>
       <c r="B68" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>129224134</v>
       </c>
       <c r="B69" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -6948,7 +6948,7 @@
         <v>129224130</v>
       </c>
       <c r="B65" t="n">
-        <v>91549</v>
+        <v>91577</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>129224131</v>
       </c>
       <c r="B66" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>129224133</v>
       </c>
       <c r="B67" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>129224129</v>
       </c>
       <c r="B68" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>129224134</v>
       </c>
       <c r="B69" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>56823811</v>
       </c>
       <c r="B2" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>679624.8264518311</v>
+        <v>679625</v>
       </c>
       <c r="R2" t="n">
-        <v>7118355.174492942</v>
+        <v>7118355</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2015-05-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56823810</v>
+        <v>129224130</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,34 +793,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gålgoberget, Ly lm</t>
+          <t>Vargträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>679624.8264518311</v>
+        <v>679702</v>
       </c>
       <c r="R3" t="n">
-        <v>7118355.174492942</v>
+        <v>7118430</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,22 +851,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,36 +872,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128458343</v>
+        <v>128472149</v>
       </c>
       <c r="B4" t="n">
-        <v>56913</v>
+        <v>92632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>679724</v>
+        <v>679727</v>
       </c>
       <c r="R4" t="n">
-        <v>7118278</v>
+        <v>7118309</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,22 +973,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Felix Gustafsson</t>
+          <t>Felix Gustafsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128458651</v>
+        <v>129224133</v>
       </c>
       <c r="B5" t="n">
-        <v>97516</v>
+        <v>92632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,34 +996,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gålgoberget, Ly lm</t>
+          <t>Vargträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>679660</v>
+        <v>679718</v>
       </c>
       <c r="R5" t="n">
-        <v>7118198</v>
+        <v>7118300</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,12 +1054,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,69 +1079,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Felix Gustafsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128458639</v>
+        <v>128458338</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>679614</v>
+        <v>679591</v>
       </c>
       <c r="R6" t="n">
-        <v>7118176</v>
+        <v>7118426</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,32 +1188,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128458646</v>
+        <v>128458339</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1257,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>679701</v>
+        <v>679682</v>
       </c>
       <c r="R7" t="n">
-        <v>7118347</v>
+        <v>7118294</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,11 +1259,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre hack på låga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,32 +1285,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128458393</v>
+        <v>128472148</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1359,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>679637</v>
+        <v>679727</v>
       </c>
       <c r="R8" t="n">
-        <v>7118460</v>
+        <v>7118380</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,65 +1370,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Felix Gustafsson</t>
+          <t>Felix Gustafsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128458355</v>
+        <v>128472158</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>679614</v>
+        <v>679640</v>
       </c>
       <c r="R9" t="n">
-        <v>7118447</v>
+        <v>7118398</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,11 +1455,6 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1519,44 +1467,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Felix Gustafsson</t>
+          <t>Felix Gustafsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128458379</v>
+        <v>56823810</v>
       </c>
       <c r="B10" t="n">
-        <v>58093</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1514,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>679582</v>
+        <v>679625</v>
       </c>
       <c r="R10" t="n">
-        <v>7118432</v>
+        <v>7118355</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,12 +1544,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,48 +1560,58 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Felix Gustafsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128458380</v>
+        <v>128458383</v>
       </c>
       <c r="B11" t="n">
-        <v>91533</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1621,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>679630</v>
+        <v>679564</v>
       </c>
       <c r="R11" t="n">
-        <v>7118401</v>
+        <v>7118347</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,12 +1659,18 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Apotecier</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1728,11 +1692,11 @@
         <v>128458390</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1822,32 +1786,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128458361</v>
+        <v>128458391</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>679603</v>
+        <v>679610</v>
       </c>
       <c r="R13" t="n">
-        <v>7118423</v>
+        <v>7118293</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1893,11 +1857,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,10 +1883,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128458666</v>
+        <v>128458392</v>
       </c>
       <c r="B14" t="n">
-        <v>98645</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,46 +1894,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>679677</v>
+        <v>679587</v>
       </c>
       <c r="R14" t="n">
-        <v>7118227</v>
+        <v>7118403</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2009,18 +1956,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Blomställning</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2039,14 +1980,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128458684</v>
+        <v>128458393</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2074,10 +2015,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>679669</v>
+        <v>679637</v>
       </c>
       <c r="R15" t="n">
-        <v>7118266</v>
+        <v>7118460</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,32 +2077,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128458345</v>
+        <v>128458394</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,10 +2112,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>679629</v>
+        <v>679604</v>
       </c>
       <c r="R16" t="n">
-        <v>7118222</v>
+        <v>7118405</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,32 +2174,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128458348</v>
+        <v>128458395</v>
       </c>
       <c r="B17" t="n">
-        <v>57883</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2268,10 +2209,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>679621</v>
+        <v>679643</v>
       </c>
       <c r="R17" t="n">
-        <v>7118452</v>
+        <v>7118369</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,32 +2271,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128458339</v>
+        <v>128458396</v>
       </c>
       <c r="B18" t="n">
-        <v>91480</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2365,10 +2306,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>679682</v>
+        <v>679612</v>
       </c>
       <c r="R18" t="n">
-        <v>7118294</v>
+        <v>7118334</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,14 +2368,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128458392</v>
+        <v>128458397</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2462,10 +2403,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>679587</v>
+        <v>679666</v>
       </c>
       <c r="R19" t="n">
-        <v>7118403</v>
+        <v>7118288</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2524,32 +2465,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128458352</v>
+        <v>128458398</v>
       </c>
       <c r="B20" t="n">
-        <v>57720</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2559,10 +2500,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>679621</v>
+        <v>679689</v>
       </c>
       <c r="R20" t="n">
-        <v>7118452</v>
+        <v>7118284</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2621,32 +2562,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128458400</v>
+        <v>128458669</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2656,10 +2597,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>679599</v>
+        <v>679615</v>
       </c>
       <c r="R21" t="n">
-        <v>7118424</v>
+        <v>7118231</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2696,7 +2637,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Bohål på granlåga</t>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2705,6 +2646,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2723,14 +2665,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128458690</v>
+        <v>128458682</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2758,10 +2700,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>679678</v>
+        <v>679705</v>
       </c>
       <c r="R22" t="n">
-        <v>7118225</v>
+        <v>7118324</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2820,14 +2762,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128458396</v>
+        <v>128458683</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2855,10 +2797,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>679612</v>
+        <v>679678</v>
       </c>
       <c r="R23" t="n">
-        <v>7118334</v>
+        <v>7118309</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2917,14 +2859,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128458383</v>
+        <v>128458684</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2952,10 +2894,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>679564</v>
+        <v>679669</v>
       </c>
       <c r="R24" t="n">
-        <v>7118347</v>
+        <v>7118266</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2990,18 +2932,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Apotecier</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3020,14 +2956,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128458688</v>
+        <v>128458685</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3055,10 +2991,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>679619</v>
+        <v>679565</v>
       </c>
       <c r="R25" t="n">
-        <v>7118185</v>
+        <v>7118208</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3120,11 +3056,11 @@
         <v>128458686</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3214,32 +3150,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128458360</v>
+        <v>128458687</v>
       </c>
       <c r="B27" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3249,10 +3185,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>679584</v>
+        <v>679610</v>
       </c>
       <c r="R27" t="n">
-        <v>7118426</v>
+        <v>7118162</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3285,11 +3221,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3316,32 +3247,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128458667</v>
+        <v>128458688</v>
       </c>
       <c r="B28" t="n">
-        <v>82988</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3282,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>679624</v>
+        <v>679619</v>
       </c>
       <c r="R28" t="n">
-        <v>7118176</v>
+        <v>7118185</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3413,32 +3344,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128458347</v>
+        <v>128458689</v>
       </c>
       <c r="B29" t="n">
-        <v>57883</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3448,10 +3379,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>679582</v>
+        <v>679651</v>
       </c>
       <c r="R29" t="n">
-        <v>7118432</v>
+        <v>7118207</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3510,14 +3441,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128458397</v>
+        <v>128458690</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3545,10 +3476,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>679666</v>
+        <v>679678</v>
       </c>
       <c r="R30" t="n">
-        <v>7118288</v>
+        <v>7118225</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3607,14 +3538,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128458683</v>
+        <v>128472167</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3642,10 +3573,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>679678</v>
+        <v>679677</v>
       </c>
       <c r="R31" t="n">
-        <v>7118309</v>
+        <v>7118405</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3692,44 +3623,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Felix Gustafsson</t>
+          <t>Felix Gustafsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128458363</v>
+        <v>128472168</v>
       </c>
       <c r="B32" t="n">
-        <v>80162</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3739,10 +3670,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>679619</v>
+        <v>679667</v>
       </c>
       <c r="R32" t="n">
-        <v>7118451</v>
+        <v>7118389</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3789,26 +3720,26 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Felix Gustafsson</t>
+          <t>Felix Gustafsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128458395</v>
+        <v>128472169</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3836,10 +3767,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>679643</v>
+        <v>679722</v>
       </c>
       <c r="R33" t="n">
-        <v>7118369</v>
+        <v>7118390</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3886,44 +3817,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Felix Gustafsson</t>
+          <t>Felix Gustafsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128458649</v>
+        <v>128472170</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3933,10 +3864,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>679607</v>
+        <v>679711</v>
       </c>
       <c r="R34" t="n">
-        <v>7118183</v>
+        <v>7118370</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3971,11 +3902,6 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -3988,26 +3914,26 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Felix Gustafsson</t>
+          <t>Felix Gustafsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128458689</v>
+        <v>128472172</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4035,10 +3961,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>679651</v>
+        <v>679688</v>
       </c>
       <c r="R35" t="n">
-        <v>7118207</v>
+        <v>7118409</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4085,44 +4011,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Felix Gustafsson</t>
+          <t>Felix Gustafsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128458669</v>
+        <v>128458667</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>83290</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4132,10 +4058,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>679615</v>
+        <v>679624</v>
       </c>
       <c r="R36" t="n">
-        <v>7118231</v>
+        <v>7118176</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4170,18 +4096,12 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4200,10 +4120,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128458341</v>
+        <v>128501348</v>
       </c>
       <c r="B37" t="n">
-        <v>79648</v>
+        <v>83307</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4211,34 +4131,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>679625</v>
+        <v>679619</v>
       </c>
       <c r="R37" t="n">
-        <v>7118333</v>
+        <v>7118446</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4279,6 +4202,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4290,17 +4214,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Felix Gustafsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128458650</v>
+        <v>128458341</v>
       </c>
       <c r="B38" t="n">
-        <v>57723</v>
+        <v>79946</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4308,21 +4232,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4332,10 +4256,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>679651</v>
+        <v>679625</v>
       </c>
       <c r="R38" t="n">
-        <v>7118217</v>
+        <v>7118333</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4368,11 +4292,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4399,32 +4318,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128458357</v>
+        <v>128458363</v>
       </c>
       <c r="B39" t="n">
-        <v>57723</v>
+        <v>80460</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4434,10 +4353,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>679576</v>
+        <v>679619</v>
       </c>
       <c r="R39" t="n">
-        <v>7118418</v>
+        <v>7118451</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4470,11 +4389,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4501,10 +4415,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128458338</v>
+        <v>128472159</v>
       </c>
       <c r="B40" t="n">
-        <v>91480</v>
+        <v>80460</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4512,21 +4426,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6461</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4536,10 +4450,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>679591</v>
+        <v>679749</v>
       </c>
       <c r="R40" t="n">
-        <v>7118426</v>
+        <v>7118408</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4586,44 +4500,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Felix Gustafsson</t>
+          <t>Felix Gustafsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128458685</v>
+        <v>128458352</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>57950</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4633,10 +4547,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>679565</v>
+        <v>679621</v>
       </c>
       <c r="R41" t="n">
-        <v>7118208</v>
+        <v>7118452</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4695,32 +4609,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128458398</v>
+        <v>128458646</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>57950</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4730,10 +4644,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>679689</v>
+        <v>679701</v>
       </c>
       <c r="R42" t="n">
-        <v>7118284</v>
+        <v>7118347</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4766,6 +4680,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre hack på låga</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4795,7 +4714,7 @@
         <v>128458354</v>
       </c>
       <c r="B43" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4894,10 +4813,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128458359</v>
+        <v>128458355</v>
       </c>
       <c r="B44" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4923,16 +4842,24 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>679602</v>
+        <v>679614</v>
       </c>
       <c r="R44" t="n">
-        <v>7118340</v>
+        <v>7118447</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4969,7 +4896,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4996,27 +4923,27 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128458665</v>
+        <v>128458357</v>
       </c>
       <c r="B45" t="n">
-        <v>58093</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5031,10 +4958,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>679618</v>
+        <v>679576</v>
       </c>
       <c r="R45" t="n">
-        <v>7118186</v>
+        <v>7118418</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5071,7 +4998,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>läte</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5098,10 +5025,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128458394</v>
+        <v>128458359</v>
       </c>
       <c r="B46" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5109,21 +5036,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5133,10 +5060,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>679604</v>
+        <v>679602</v>
       </c>
       <c r="R46" t="n">
-        <v>7118405</v>
+        <v>7118340</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5169,6 +5096,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5195,10 +5127,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128458682</v>
+        <v>128458360</v>
       </c>
       <c r="B47" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5206,21 +5138,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5230,10 +5162,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>679705</v>
+        <v>679584</v>
       </c>
       <c r="R47" t="n">
-        <v>7118324</v>
+        <v>7118426</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5266,6 +5198,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5292,10 +5229,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128458391</v>
+        <v>128458361</v>
       </c>
       <c r="B48" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5303,21 +5240,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5327,10 +5264,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>679610</v>
+        <v>679603</v>
       </c>
       <c r="R48" t="n">
-        <v>7118293</v>
+        <v>7118423</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5363,6 +5300,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5389,32 +5331,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128472156</v>
+        <v>128458400</v>
       </c>
       <c r="B49" t="n">
-        <v>97517</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5424,10 +5366,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>679705</v>
+        <v>679599</v>
       </c>
       <c r="R49" t="n">
-        <v>7118311</v>
+        <v>7118424</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5462,6 +5404,11 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Bohål på granlåga</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5474,22 +5421,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128472170</v>
+        <v>128458649</v>
       </c>
       <c r="B50" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5497,21 +5444,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5521,10 +5468,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>679711</v>
+        <v>679607</v>
       </c>
       <c r="R50" t="n">
-        <v>7118370</v>
+        <v>7118183</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5559,6 +5506,11 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5571,44 +5523,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128472174</v>
+        <v>128458650</v>
       </c>
       <c r="B51" t="n">
-        <v>98563</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5570,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>679749</v>
+        <v>679651</v>
       </c>
       <c r="R51" t="n">
-        <v>7118381</v>
+        <v>7118217</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5656,6 +5608,11 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5668,22 +5625,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128472149</v>
+        <v>128458343</v>
       </c>
       <c r="B52" t="n">
-        <v>92213</v>
+        <v>57141</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5691,21 +5648,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3298</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5715,10 +5672,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>679727</v>
+        <v>679724</v>
       </c>
       <c r="R52" t="n">
-        <v>7118309</v>
+        <v>7118278</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5765,22 +5722,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128472158</v>
+        <v>128458379</v>
       </c>
       <c r="B53" t="n">
-        <v>91480</v>
+        <v>58327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5788,21 +5745,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5812,10 +5769,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>679640</v>
+        <v>679582</v>
       </c>
       <c r="R53" t="n">
-        <v>7118398</v>
+        <v>7118432</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5862,44 +5819,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128472169</v>
+        <v>128458665</v>
       </c>
       <c r="B54" t="n">
-        <v>79029</v>
+        <v>58327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5909,10 +5866,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>679722</v>
+        <v>679618</v>
       </c>
       <c r="R54" t="n">
-        <v>7118390</v>
+        <v>7118186</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5947,6 +5904,11 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>läte</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -5959,22 +5921,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128472165</v>
+        <v>128472166</v>
       </c>
       <c r="B55" t="n">
-        <v>57827</v>
+        <v>58327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5982,16 +5944,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103031</v>
+        <v>103015</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6006,10 +5968,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>679747</v>
+        <v>679731</v>
       </c>
       <c r="R55" t="n">
-        <v>7118413</v>
+        <v>7118423</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6068,10 +6030,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128472166</v>
+        <v>128472171</v>
       </c>
       <c r="B56" t="n">
-        <v>58093</v>
+        <v>58327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6103,10 +6065,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>679731</v>
+        <v>679663</v>
       </c>
       <c r="R56" t="n">
-        <v>7118423</v>
+        <v>7118432</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6165,32 +6127,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128472148</v>
+        <v>128458345</v>
       </c>
       <c r="B57" t="n">
-        <v>91480</v>
+        <v>58114</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6200,10 +6162,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>679727</v>
+        <v>679629</v>
       </c>
       <c r="R57" t="n">
-        <v>7118380</v>
+        <v>7118222</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6250,22 +6212,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128472172</v>
+        <v>128458347</v>
       </c>
       <c r="B58" t="n">
-        <v>79029</v>
+        <v>58114</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6273,21 +6235,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6297,10 +6259,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>679688</v>
+        <v>679582</v>
       </c>
       <c r="R58" t="n">
-        <v>7118409</v>
+        <v>7118432</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6347,44 +6309,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128472159</v>
+        <v>128458348</v>
       </c>
       <c r="B59" t="n">
-        <v>80162</v>
+        <v>58114</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6394,10 +6356,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>679749</v>
+        <v>679621</v>
       </c>
       <c r="R59" t="n">
-        <v>7118408</v>
+        <v>7118452</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6444,57 +6406,69 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128472157</v>
+        <v>128458639</v>
       </c>
       <c r="B60" t="n">
-        <v>97517</v>
+        <v>58114</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>679659</v>
+        <v>679614</v>
       </c>
       <c r="R60" t="n">
-        <v>7118444</v>
+        <v>7118176</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6541,39 +6515,39 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128472171</v>
+        <v>128472165</v>
       </c>
       <c r="B61" t="n">
-        <v>58093</v>
+        <v>58057</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103015</v>
+        <v>103031</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6588,10 +6562,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>679663</v>
+        <v>679747</v>
       </c>
       <c r="R61" t="n">
-        <v>7118432</v>
+        <v>7118413</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6650,32 +6624,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128472168</v>
+        <v>128472174</v>
       </c>
       <c r="B62" t="n">
-        <v>79029</v>
+        <v>99035</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6685,10 +6659,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>679667</v>
+        <v>679749</v>
       </c>
       <c r="R62" t="n">
-        <v>7118389</v>
+        <v>7118381</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6747,35 +6721,47 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128472167</v>
+        <v>128458666</v>
       </c>
       <c r="B63" t="n">
-        <v>79029</v>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
@@ -6785,7 +6771,7 @@
         <v>679677</v>
       </c>
       <c r="R63" t="n">
-        <v>7118405</v>
+        <v>7118227</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6820,72 +6806,75 @@
           <t>2025-09-14</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Blomställning</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128501348</v>
+        <v>128458651</v>
       </c>
       <c r="B64" t="n">
-        <v>83010</v>
+        <v>97983</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>679619</v>
+        <v>679660</v>
       </c>
       <c r="R64" t="n">
-        <v>7118446</v>
+        <v>7118198</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6926,7 +6915,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6938,56 +6926,52 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129224130</v>
+        <v>128472156</v>
       </c>
       <c r="B65" t="n">
-        <v>91577</v>
+        <v>97983</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1108</v>
+        <v>221945</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Vargträsk, Ly lm</t>
+          <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>679702</v>
+        <v>679705</v>
       </c>
       <c r="R65" t="n">
-        <v>7118430</v>
+        <v>7118311</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7014,17 +6998,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7039,57 +7018,57 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Felix Gustafsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129224131</v>
+        <v>128472157</v>
       </c>
       <c r="B66" t="n">
-        <v>91601</v>
+        <v>97983</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Vargträsk, Ly lm</t>
+          <t>Gålgoberget, Ly lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>679728</v>
+        <v>679659</v>
       </c>
       <c r="R66" t="n">
-        <v>7118383</v>
+        <v>7118444</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7116,17 +7095,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7141,325 +7115,15 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Felix Gustafsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>129224133</v>
-      </c>
-      <c r="B67" t="n">
-        <v>92299</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Vargträsk, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>679718</v>
-      </c>
-      <c r="R67" t="n">
-        <v>7118300</v>
-      </c>
-      <c r="S67" t="n">
-        <v>10</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Örträsk</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>129224129</v>
-      </c>
-      <c r="B68" t="n">
-        <v>91601</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Vargträsk, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>679626</v>
-      </c>
-      <c r="R68" t="n">
-        <v>7118415</v>
-      </c>
-      <c r="S68" t="n">
-        <v>10</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Örträsk</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>129224134</v>
-      </c>
-      <c r="B69" t="n">
-        <v>91601</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Vargträsk, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>679694</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7118257</v>
-      </c>
-      <c r="S69" t="n">
-        <v>10</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Örträsk</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41223-2024 artfynd.xlsx
+++ b/artfynd/A 41223-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AZ66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56823811</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224130</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128472149</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224133</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458338</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458339</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128472148</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128472158</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1583,6 +1628,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56823810</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1686,6 +1736,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458383</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458390</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1880,6 +1940,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458391</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1977,6 +2042,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458392</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2074,6 +2144,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458393</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2171,6 +2246,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458394</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2268,6 +2348,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458395</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2365,6 +2450,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458396</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2462,6 +2552,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458397</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2559,6 +2654,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458398</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2662,6 +2762,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458669</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2759,6 +2864,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458682</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2856,6 +2966,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458683</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2953,6 +3068,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458684</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3050,6 +3170,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458685</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3147,6 +3272,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458686</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3244,6 +3374,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458687</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3341,6 +3476,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458688</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3438,6 +3578,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458689</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3535,6 +3680,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458690</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3632,6 +3782,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128472167</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3729,6 +3884,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128472168</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3826,6 +3986,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128472169</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3923,6 +4088,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128472170</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4020,6 +4190,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128472172</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4117,6 +4292,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458667</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4218,6 +4398,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128501348</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4315,6 +4500,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458341</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4412,6 +4602,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458363</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4509,6 +4704,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128472159</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4606,6 +4806,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458352</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4708,6 +4913,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458646</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4810,6 +5020,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458354</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4920,6 +5135,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458355</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5022,6 +5242,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458357</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5124,6 +5349,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458359</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5226,6 +5456,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458360</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5328,6 +5563,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458361</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5430,6 +5670,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458400</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5532,6 +5777,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458649</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5634,6 +5884,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458650</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5731,6 +5986,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458343</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5828,6 +6088,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458379</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5930,6 +6195,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458665</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6027,6 +6297,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128472166</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6124,6 +6399,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128472171</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6221,6 +6501,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458345</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6318,6 +6603,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458347</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6415,6 +6705,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458348</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6524,6 +6819,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458639</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6621,6 +6921,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128472165</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6718,6 +7023,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128472174</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6833,6 +7143,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458666</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6930,6 +7245,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128458651</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7027,6 +7347,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128472156</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7124,8 +7449,80 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128472157</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>